--- a/results_logic/Results_By_Sector.xlsx
+++ b/results_logic/Results_By_Sector.xlsx
@@ -25,12 +25,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telecommunication" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textiles" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wellness" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Financial Services'!$A$2:$BA$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Financial Services'!$A$2:$BA$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Other Textile Products'!$A$2:$BA$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fast Moving Consumer Goods'!$A$2:$BA$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fertilizers'!$A$2:$BA$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fast Moving Consumer Goods'!$A$2:$BA$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fertilizers'!$A$2:$BA$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Information Technology'!$A$2:$BA$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Realty'!$A$2:$BA$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Media, Entertainment &amp; Publicat'!$A$2:$BA$12</definedName>
@@ -44,6 +45,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Services'!$A$2:$BA$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Telecommunication'!$A$2:$BA$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Textiles'!$A$2:$BA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Wellness'!$A$2:$BA$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -712,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -853,61 +855,61 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>41.5</v>
+        <v>40.9</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>39</v>
+        <v>40.6</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>39.2</v>
+        <v>46.6</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>12.7</v>
+        <v>20.4</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>-0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>1521.6</v>
+        <v>1443.1</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>63.2</v>
+        <v>63.9</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>6.1</v>
+        <v>9.6</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>-31.9</v>
+        <v>-29.4</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>-21</v>
+        <v>-19.7</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>5283.3</v>
+        <v>5022</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1105,381 +1107,369 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>59.2</v>
+        <v>50.5</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>105.2</v>
+        <v>74.8</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>152.1</v>
+        <v>210.9</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>76.3</v>
+        <v>157</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>2</v>
+        <v>13.6</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <v>0.7</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>331.5</v>
+        <v>224.5</v>
       </c>
       <c r="K7" s="17" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>32.8</v>
+        <v>25.2</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>70.2</v>
+        <v>72.3</v>
       </c>
       <c r="N7" s="17" t="n">
-        <v>84.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="O7" s="17" t="n">
-        <v>107.6</v>
+        <v>126.1</v>
       </c>
       <c r="P7" s="17" t="n">
-        <v>53.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="Q7" s="19" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>43</v>
+        <v>31.3</v>
       </c>
       <c r="S7" s="18" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="T7" s="17" t="n">
-        <v>678</v>
+        <v>452.9</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Wellness</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>-77.2</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-33.4</v>
+        <v>37.5</v>
+      </c>
+      <c r="D8" s="36" t="inlineStr"/>
+      <c r="E8" s="36" t="inlineStr"/>
+      <c r="F8" s="36" t="inlineStr"/>
+      <c r="G8" s="19" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="17" t="n">
-        <v>21.3</v>
+        <v>18.6</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>61.2</v>
+        <v>20.8</v>
       </c>
       <c r="K8" s="17" t="n">
-        <v>248.3</v>
+        <v>9.6</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>126.8</v>
+        <v>125</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="N8" s="19" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>-31.1</v>
-      </c>
-      <c r="P8" s="17" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="Q8" s="22" t="n">
-        <v>-91.09999999999999</v>
+        <v>32.6</v>
+      </c>
+      <c r="N8" s="36" t="inlineStr"/>
+      <c r="O8" s="36" t="inlineStr"/>
+      <c r="P8" s="36" t="inlineStr"/>
+      <c r="Q8" s="25" t="n">
+        <v>1.6</v>
       </c>
       <c r="R8" s="22" t="n">
-        <v>-31.5</v>
+        <v>-55.7</v>
       </c>
       <c r="S8" s="17" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="T8" s="17" t="n">
-        <v>212.7</v>
+        <v>3.8</v>
+      </c>
+      <c r="T8" s="22" t="n">
+        <v>-40.5</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Asset Management Company</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>24.6</v>
+        <v>29</v>
       </c>
       <c r="D9" s="17" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>-64.59999999999999</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-26.8</v>
+      </c>
+      <c r="I9" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="22" t="n">
-        <v>-42.9</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>-45</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>0.9</v>
-      </c>
       <c r="J9" s="17" t="n">
-        <v>755.4</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>-4.5</v>
+        <v>54.5</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>217.9</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>4.6</v>
+        <v>111.5</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>17</v>
+        <v>25.5</v>
       </c>
       <c r="N9" s="17" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="O9" s="22" t="n">
-        <v>-35.6</v>
-      </c>
-      <c r="P9" s="22" t="n">
-        <v>-47.1</v>
-      </c>
-      <c r="Q9" s="17" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="R9" s="17" t="n">
-        <v>36.5</v>
+        <v>-17.2</v>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="Q9" s="22" t="n">
+        <v>-77.3</v>
+      </c>
+      <c r="R9" s="22" t="n">
+        <v>-25.6</v>
       </c>
       <c r="S9" s="17" t="n">
-        <v>2.7</v>
+        <v>62.7</v>
       </c>
       <c r="T9" s="17" t="n">
-        <v>2490.5</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Asset Management Company</t>
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>-13.4</v>
+        <v>24.6</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>20</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-28.3</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>-11.3</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>-7.3</v>
+        <v>-42.9</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>0.9</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>116.8</v>
+        <v>755.4</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="L10" s="18" t="n">
-        <v>-0.5</v>
+        <v>-4.5</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>4.6</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N10" s="19" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="O10" s="19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="P10" s="19" t="n">
-        <v>11.7</v>
+        <v>17</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O10" s="22" t="n">
+        <v>-35.6</v>
+      </c>
+      <c r="P10" s="22" t="n">
+        <v>-47.1</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="R10" s="19" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="S10" s="39" t="n">
-        <v>-2</v>
+        <v>65.8</v>
+      </c>
+      <c r="R10" s="17" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="S10" s="17" t="n">
+        <v>2.7</v>
       </c>
       <c r="T10" s="17" t="n">
-        <v>460.9</v>
+        <v>2490.5</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Diversified Commercial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="B11" s="21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C11" s="17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>-14.3</v>
+        <v>-13.4</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-17.3</v>
+        <v>-28.3</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-11.3</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>10.2</v>
+        <v>13</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="J11" s="39" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="L11" s="18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N11" s="19" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="O11" s="19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P11" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Q11" s="17" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="R11" s="19" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="S11" s="39" t="n">
         <v>-2</v>
       </c>
-      <c r="K11" s="22" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <v>-29.5</v>
-      </c>
-      <c r="N11" s="18" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="O11" s="19" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="P11" s="22" t="n">
-        <v>-677.3</v>
-      </c>
-      <c r="Q11" s="22" t="n">
-        <v>-895.3</v>
-      </c>
-      <c r="R11" s="22" t="n">
-        <v>-458.6</v>
-      </c>
-      <c r="S11" s="22" t="n">
-        <v>-875.9</v>
-      </c>
-      <c r="T11" s="22" t="n">
-        <v>-423.1</v>
+      <c r="T11" s="17" t="n">
+        <v>460.9</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Diversified Commercial Services</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>-4.3</v>
+        <v>3</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>-14.3</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-15</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-7.6</v>
+        <v>-16.7</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>-17.3</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>1349.9</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="N12" s="17" t="n">
-        <v>785.8</v>
-      </c>
-      <c r="O12" s="17" t="n">
-        <v>1542.8</v>
-      </c>
-      <c r="P12" s="17" t="n">
-        <v>776.2</v>
-      </c>
-      <c r="Q12" s="19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="R12" s="19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="S12" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" s="17" t="n">
-        <v>5180</v>
+        <v>10.2</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="J12" s="39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="L12" s="22" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="N12" s="18" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="O12" s="19" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="P12" s="22" t="n">
+        <v>-677.3</v>
+      </c>
+      <c r="Q12" s="22" t="n">
+        <v>-895.3</v>
+      </c>
+      <c r="R12" s="22" t="n">
+        <v>-458.6</v>
+      </c>
+      <c r="S12" s="22" t="n">
+        <v>-875.9</v>
+      </c>
+      <c r="T12" s="22" t="n">
+        <v>-423.1</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1489,1618 +1479,1734 @@
         </is>
       </c>
       <c r="B13" s="21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>1838.6</v>
+        <v>1746.8</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="L13" s="22" t="n">
-        <v>-2.1</v>
+        <v>-6.5</v>
+      </c>
+      <c r="L13" s="39" t="n">
+        <v>-2</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
       <c r="N13" s="19" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="O13" s="17" t="n">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="P13" s="19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Q13" s="17" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="R13" s="17" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="S13" s="17" t="n">
         <v>6.8</v>
       </c>
-      <c r="Q13" s="17" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="R13" s="17" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="S13" s="17" t="n">
-        <v>7.1</v>
-      </c>
       <c r="T13" s="17" t="n">
-        <v>5133.9</v>
+        <v>4910.7</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>-16.6</v>
+      <c r="C14" s="19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>-4.3</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-36.6</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-18.6</v>
-      </c>
-      <c r="G14" s="17" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>-11.4</v>
+        <v>-15</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>-0.8</v>
       </c>
       <c r="J14" s="17" t="n">
-        <v>142</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L14" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N14" s="18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O14" s="24" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="P14" s="18" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="R14" s="17" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="S14" s="22" t="n">
-        <v>-5</v>
+        <v>1349.9</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>785.8</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>1542.8</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>776.2</v>
+      </c>
+      <c r="Q14" s="19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="R14" s="19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="T14" s="17" t="n">
-        <v>565.9</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="B15" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D15" s="38" t="inlineStr"/>
-      <c r="E15" s="38" t="inlineStr"/>
-      <c r="F15" s="38" t="inlineStr"/>
-      <c r="G15" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L15" s="17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M15" s="25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N15" s="38" t="inlineStr"/>
-      <c r="O15" s="38" t="inlineStr"/>
-      <c r="P15" s="38" t="inlineStr"/>
-      <c r="Q15" s="25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R15" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="S15" s="17" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>142</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N15" s="18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O15" s="24" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="P15" s="18" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="Q15" s="17" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="R15" s="17" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S15" s="22" t="n">
+        <v>-5</v>
       </c>
       <c r="T15" s="17" t="n">
-        <v>2</v>
+        <v>565.9</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C16" s="25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>13418.2</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>-3.4</v>
+        <v>3.1</v>
+      </c>
+      <c r="D16" s="36" t="inlineStr"/>
+      <c r="E16" s="36" t="inlineStr"/>
+      <c r="F16" s="36" t="inlineStr"/>
+      <c r="G16" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J16" s="22" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>0.4</v>
       </c>
       <c r="L16" s="17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N16" s="19" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O16" s="25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P16" s="25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" s="17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="R16" s="19" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="S16" s="18" t="n">
-        <v>-0.5</v>
+        <v>5.8</v>
+      </c>
+      <c r="M16" s="25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N16" s="36" t="inlineStr"/>
+      <c r="O16" s="36" t="inlineStr"/>
+      <c r="P16" s="36" t="inlineStr"/>
+      <c r="Q16" s="25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R16" s="22" t="n">
+        <v>-20</v>
+      </c>
+      <c r="S16" s="17" t="n">
+        <v>3.2</v>
       </c>
       <c r="T16" s="17" t="n">
-        <v>51069.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Furniture, Home Furnishing</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="B17" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>-7</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>-26.6</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-14.8</v>
+        <v>5</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>-6.9</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I17" s="22" t="n">
-        <v>-2.3</v>
+        <v>14.9</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>-0.9</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>0.2</v>
+        <v>13418.2</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>-3.4</v>
       </c>
       <c r="L17" s="17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>29</v>
+        <v>2.2</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <v>14.2</v>
       </c>
       <c r="N17" s="19" t="n">
-        <v>5.2</v>
+        <v>8.9</v>
       </c>
       <c r="O17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="18" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="Q17" s="19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R17" s="17" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S17" s="22" t="n">
-        <v>-2.1</v>
+        <v>3.8</v>
+      </c>
+      <c r="P17" s="25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" s="17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="R17" s="19" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="S17" s="18" t="n">
+        <v>-0.5</v>
       </c>
       <c r="T17" s="17" t="n">
-        <v>83.3</v>
+        <v>51069.1</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Media, Entertainment &amp; Publication</t>
+          <t>Furniture, Home Furnishing</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>-16.1</v>
+        <v>2</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>-7</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>-27.4</v>
+        <v>-26.6</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-39.2</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>-47.1</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>-34.2</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>-20.3</v>
+        <v>-30</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>15.2</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>-43.5</v>
+        <v>-2.3</v>
       </c>
       <c r="J18" s="17" t="n">
-        <v>133.9</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>-47.2</v>
-      </c>
-      <c r="L18" s="22" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="N18" s="22" t="n">
-        <v>-19.8</v>
-      </c>
-      <c r="O18" s="24" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="P18" s="24" t="n">
-        <v>-12.4</v>
+        <v>53.6</v>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="N18" s="19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="18" t="n">
+        <v>-1.4</v>
       </c>
       <c r="Q18" s="19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R18" s="18" t="n">
-        <v>-1.4</v>
+        <v>5.6</v>
+      </c>
+      <c r="R18" s="17" t="n">
+        <v>25.2</v>
       </c>
       <c r="S18" s="22" t="n">
-        <v>-6.7</v>
+        <v>-2.1</v>
       </c>
       <c r="T18" s="17" t="n">
-        <v>635.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Media, Entertainment &amp; Publication</t>
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>-82.5</v>
-      </c>
-      <c r="D19" s="38" t="inlineStr"/>
-      <c r="E19" s="38" t="inlineStr"/>
+        <v>-16.1</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>-39.2</v>
+      </c>
       <c r="F19" s="22" t="n">
-        <v>-41.8</v>
+        <v>-47.1</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>-49.4</v>
+        <v>-34.2</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>-27.4</v>
+        <v>-20.3</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>-50.7</v>
+        <v>-43.5</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>123.7</v>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v>4.5</v>
+        <v>133.9</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>-47.2</v>
       </c>
       <c r="L19" s="22" t="n">
-        <v>-40.8</v>
+        <v>-23.3</v>
       </c>
       <c r="M19" s="22" t="n">
-        <v>-87.59999999999999</v>
-      </c>
-      <c r="N19" s="38" t="inlineStr"/>
-      <c r="O19" s="38" t="inlineStr"/>
-      <c r="P19" s="22" t="n">
-        <v>-75.90000000000001</v>
-      </c>
-      <c r="Q19" s="22" t="n">
-        <v>-72.09999999999999</v>
-      </c>
-      <c r="R19" s="22" t="n">
-        <v>-85</v>
+        <v>-18.2</v>
+      </c>
+      <c r="N19" s="22" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="O19" s="24" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="P19" s="24" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="Q19" s="19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R19" s="18" t="n">
+        <v>-1.4</v>
       </c>
       <c r="S19" s="22" t="n">
-        <v>-81.7</v>
+        <v>-6.7</v>
       </c>
       <c r="T19" s="17" t="n">
-        <v>4417.8</v>
+        <v>635.5</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Other Textile Products</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="B20" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="36" t="inlineStr"/>
+      <c r="C20" s="22" t="n">
+        <v>-82.5</v>
+      </c>
       <c r="D20" s="36" t="inlineStr"/>
       <c r="E20" s="36" t="inlineStr"/>
-      <c r="F20" s="36" t="inlineStr"/>
-      <c r="G20" s="17" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="I20" s="36" t="inlineStr"/>
-      <c r="J20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="36" t="inlineStr"/>
-      <c r="L20" s="36" t="inlineStr"/>
-      <c r="M20" s="36" t="inlineStr"/>
+      <c r="F20" s="22" t="n">
+        <v>-41.8</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>-49.4</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L20" s="22" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="M20" s="22" t="n">
+        <v>-87.59999999999999</v>
+      </c>
       <c r="N20" s="36" t="inlineStr"/>
       <c r="O20" s="36" t="inlineStr"/>
-      <c r="P20" s="36" t="inlineStr"/>
-      <c r="Q20" s="19" t="n">
+      <c r="P20" s="22" t="n">
+        <v>-75.90000000000001</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>-72.09999999999999</v>
+      </c>
+      <c r="R20" s="22" t="n">
+        <v>-85</v>
+      </c>
+      <c r="S20" s="22" t="n">
+        <v>-81.7</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>4417.8</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>Other Textile Products</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="38" t="inlineStr"/>
+      <c r="D21" s="38" t="inlineStr"/>
+      <c r="E21" s="38" t="inlineStr"/>
+      <c r="F21" s="38" t="inlineStr"/>
+      <c r="G21" s="17" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I21" s="38" t="inlineStr"/>
+      <c r="J21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="38" t="inlineStr"/>
+      <c r="L21" s="38" t="inlineStr"/>
+      <c r="M21" s="38" t="inlineStr"/>
+      <c r="N21" s="38" t="inlineStr"/>
+      <c r="O21" s="38" t="inlineStr"/>
+      <c r="P21" s="38" t="inlineStr"/>
+      <c r="Q21" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="R20" s="19" t="n">
+      <c r="R21" s="19" t="n">
         <v>7.2</v>
       </c>
-      <c r="S20" s="36" t="inlineStr"/>
-      <c r="T20" s="19" t="n">
+      <c r="S21" s="38" t="inlineStr"/>
+      <c r="T21" s="19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>▶  Delta vs Broad Market Avg (Sector Avg − Market Avg)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Companies</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Avg Sales YoY Q%</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Avg EBITDA YoY Q%</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Avg NP YoY Q%</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Avg EPS YoY Q%</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Avg EBITDA Margin%</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Avg PAT Margin%</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Avg EBITDA Margin YoY pp</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Avg PAT Margin YoY pp</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Avg EBITDA Margin QoQ pp</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>Avg PAT Margin QoQ pp</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Avg FY Sales YoY%</t>
         </is>
       </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>Avg FY EBITDA YoY%</t>
         </is>
       </c>
-      <c r="O23" s="10" t="inlineStr">
+      <c r="O24" s="10" t="inlineStr">
         <is>
           <t>Avg FY NP YoY%</t>
         </is>
       </c>
-      <c r="P23" s="10" t="inlineStr">
+      <c r="P24" s="10" t="inlineStr">
         <is>
           <t>Avg FY EPS YoY%</t>
         </is>
       </c>
-      <c r="Q23" s="10" t="inlineStr">
+      <c r="Q24" s="10" t="inlineStr">
         <is>
           <t>Avg FY EBITDA Margin%</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr">
+      <c r="R24" s="10" t="inlineStr">
         <is>
           <t>Avg FY PAT Margin%</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>Avg FY EBITDA Margin YoY pp</t>
         </is>
       </c>
-      <c r="T23" s="10" t="inlineStr">
+      <c r="T24" s="10" t="inlineStr">
         <is>
           <t>Avg FY PAT Margin YoY pp</t>
         </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="27" t="n">
-        <v>542.3</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>-38.4</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>-38.6</v>
-      </c>
-      <c r="F24" s="28" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="H24" s="27" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="I24" s="27" t="n">
-        <v>279.7</v>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>-1239.8</v>
-      </c>
-      <c r="K24" s="29" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="L24" s="29" t="n">
-        <v>-19.9</v>
-      </c>
-      <c r="M24" s="27" t="n">
-        <v>177.1</v>
-      </c>
-      <c r="N24" s="29" t="n">
-        <v>-39.6</v>
-      </c>
-      <c r="O24" s="29" t="n">
-        <v>-61.4</v>
-      </c>
-      <c r="P24" s="28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q24" s="27" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="R24" s="27" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="S24" s="27" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="T24" s="29" t="n">
-        <v>-5136.3</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>Realty</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="n">
-        <v>2</v>
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="C25" s="27" t="n">
-        <v>295.5</v>
-      </c>
-      <c r="D25" s="27" t="n">
-        <v>569.4</v>
-      </c>
-      <c r="E25" s="27" t="n">
-        <v>627.4</v>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>337</v>
+        <v>542.9</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>-40</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>-46</v>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>-13.4</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="H25" s="30" t="n">
-        <v>6.9</v>
+        <v>36.4</v>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>32.2</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>12</v>
+        <v>279.4</v>
       </c>
       <c r="J25" s="29" t="n">
-        <v>-1469.2</v>
+        <v>-1161.3</v>
       </c>
       <c r="K25" s="29" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="L25" s="27" t="n">
-        <v>43.7</v>
+        <v>-4.3</v>
+      </c>
+      <c r="L25" s="29" t="n">
+        <v>-21.3</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="N25" s="27" t="n">
-        <v>25.4</v>
+        <v>176.5</v>
+      </c>
+      <c r="N25" s="29" t="n">
+        <v>-40.1</v>
       </c>
       <c r="O25" s="29" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="P25" s="30" t="n">
-        <v>11.3</v>
+        <v>-62.1</v>
+      </c>
+      <c r="P25" s="28" t="n">
+        <v>-4.5</v>
       </c>
       <c r="Q25" s="27" t="n">
-        <v>52.6</v>
+        <v>51.2</v>
       </c>
       <c r="R25" s="27" t="n">
-        <v>43.7</v>
+        <v>28.6</v>
       </c>
       <c r="S25" s="27" t="n">
-        <v>21.4</v>
+        <v>152.6</v>
       </c>
       <c r="T25" s="29" t="n">
-        <v>-5229.6</v>
+        <v>-4875</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>TV Broadcasting &amp; Software Production</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="n">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n">
         <v>2</v>
       </c>
       <c r="C26" s="27" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>-48.1</v>
-      </c>
-      <c r="E26" s="26" t="inlineStr"/>
-      <c r="F26" s="29" t="n">
-        <v>-18</v>
-      </c>
-      <c r="G26" s="29" t="n">
-        <v>-101.1</v>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>-111.9</v>
-      </c>
-      <c r="I26" s="29" t="n">
-        <v>-112.4</v>
+        <v>296.1</v>
+      </c>
+      <c r="D26" s="27" t="n">
+        <v>567.8</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>620</v>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H26" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="27" t="n">
+        <v>11.7</v>
       </c>
       <c r="J26" s="29" t="n">
-        <v>-1626.4</v>
+        <v>-1390.7</v>
       </c>
       <c r="K26" s="29" t="n">
-        <v>-149.2</v>
-      </c>
-      <c r="L26" s="29" t="n">
-        <v>-39</v>
+        <v>-13.5</v>
+      </c>
+      <c r="L26" s="27" t="n">
+        <v>42.3</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="N26" s="29" t="n">
-        <v>-41.4</v>
-      </c>
-      <c r="O26" s="26" t="inlineStr"/>
-      <c r="P26" s="32" t="n">
-        <v>-11.2</v>
+        <v>42.5</v>
+      </c>
+      <c r="N26" s="27" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O26" s="29" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="P26" s="30" t="n">
+        <v>7.8</v>
       </c>
       <c r="Q26" s="27" t="n">
-        <v>55.8</v>
+        <v>50.1</v>
       </c>
       <c r="R26" s="27" t="n">
-        <v>85.3</v>
+        <v>43.6</v>
       </c>
       <c r="S26" s="27" t="n">
-        <v>226.4</v>
+        <v>20.1</v>
       </c>
       <c r="T26" s="29" t="n">
-        <v>-5072.4</v>
+        <v>-4968.3</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>Fertilizers</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="n">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>TV Broadcasting &amp; Software Production</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
         <v>2</v>
       </c>
       <c r="C27" s="27" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="D27" s="27" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="E27" s="27" t="n">
-        <v>112.9</v>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="G27" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H27" s="30" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>-0.5</v>
+        <v>44.1</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>-49.7</v>
+      </c>
+      <c r="E27" s="26" t="inlineStr"/>
+      <c r="F27" s="29" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="G27" s="29" t="n">
+        <v>-102.1</v>
+      </c>
+      <c r="H27" s="29" t="n">
+        <v>-112.8</v>
+      </c>
+      <c r="I27" s="29" t="n">
+        <v>-112.7</v>
       </c>
       <c r="J27" s="29" t="n">
-        <v>-1190.1</v>
+        <v>-1547.9</v>
       </c>
       <c r="K27" s="29" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="L27" s="27" t="n">
-        <v>22.2</v>
+        <v>-148.6</v>
+      </c>
+      <c r="L27" s="29" t="n">
+        <v>-40.4</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="N27" s="27" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="O27" s="27" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="P27" s="27" t="n">
-        <v>47.4</v>
+        <v>33.9</v>
+      </c>
+      <c r="N27" s="29" t="n">
+        <v>-41.9</v>
+      </c>
+      <c r="O27" s="26" t="inlineStr"/>
+      <c r="P27" s="32" t="n">
+        <v>-14.7</v>
       </c>
       <c r="Q27" s="27" t="n">
-        <v>41.8</v>
+        <v>53.3</v>
       </c>
       <c r="R27" s="27" t="n">
-        <v>46.7</v>
+        <v>85.2</v>
       </c>
       <c r="S27" s="27" t="n">
-        <v>20.9</v>
+        <v>225.1</v>
       </c>
       <c r="T27" s="29" t="n">
-        <v>-4605.3</v>
+        <v>-4811.1</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Fast Moving Consumer Goods</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="C28" s="32" t="n">
-        <v>-12.8</v>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>9.6</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="E28" s="28" t="n">
-        <v>-5.8</v>
+        <v>34.2</v>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>164.3</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G28" s="29" t="n">
-        <v>-76.59999999999999</v>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>-31.5</v>
-      </c>
-      <c r="I28" s="27" t="n">
-        <v>18.8</v>
+        <v>136.6</v>
+      </c>
+      <c r="G28" s="30" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H28" s="30" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I28" s="29" t="n">
+        <v>-2.1</v>
       </c>
       <c r="J28" s="29" t="n">
-        <v>-1460.4</v>
-      </c>
-      <c r="K28" s="27" t="n">
-        <v>234.3</v>
+        <v>-1218.6</v>
+      </c>
+      <c r="K28" s="29" t="n">
+        <v>-11.2</v>
       </c>
       <c r="L28" s="27" t="n">
-        <v>116.2</v>
-      </c>
-      <c r="M28" s="34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N28" s="29" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="O28" s="29" t="n">
-        <v>-94.3</v>
+        <v>13.2</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="N28" s="27" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="O28" s="27" t="n">
+        <v>62.2</v>
       </c>
       <c r="P28" s="27" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Q28" s="29" t="n">
-        <v>-59.2</v>
-      </c>
-      <c r="R28" s="29" t="n">
-        <v>-27.8</v>
+        <v>79.8</v>
+      </c>
+      <c r="Q28" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="R28" s="27" t="n">
+        <v>34.9</v>
       </c>
       <c r="S28" s="27" t="n">
-        <v>91.8</v>
+        <v>19.1</v>
       </c>
       <c r="T28" s="29" t="n">
-        <v>-5070.6</v>
+        <v>-4569.1</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Asset Management Company</t>
-        </is>
-      </c>
-      <c r="B29" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="29" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="D29" s="29" t="n">
-        <v>-19</v>
-      </c>
-      <c r="E29" s="29" t="n">
-        <v>-82.09999999999999</v>
-      </c>
-      <c r="F29" s="29" t="n">
-        <v>-57.7</v>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>64</v>
-      </c>
-      <c r="H29" s="27" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>-1.6</v>
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="D29" s="26" t="inlineStr"/>
+      <c r="E29" s="26" t="inlineStr"/>
+      <c r="F29" s="26" t="inlineStr"/>
+      <c r="G29" s="30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="27" t="n">
+        <v>15.8</v>
       </c>
       <c r="J29" s="29" t="n">
-        <v>-766.2</v>
+        <v>-1422.3</v>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="L29" s="29" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M29" s="28" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="N29" s="29" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="O29" s="29" t="n">
-        <v>-98.8</v>
-      </c>
-      <c r="P29" s="29" t="n">
-        <v>-53.2</v>
-      </c>
+        <v>-3.8</v>
+      </c>
+      <c r="L29" s="27" t="n">
+        <v>113</v>
+      </c>
+      <c r="M29" s="30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N29" s="26" t="inlineStr"/>
+      <c r="O29" s="26" t="inlineStr"/>
+      <c r="P29" s="26" t="inlineStr"/>
       <c r="Q29" s="27" t="n">
-        <v>97.7</v>
-      </c>
-      <c r="R29" s="27" t="n">
-        <v>40.2</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="29" t="n">
+        <v>-52.1</v>
       </c>
       <c r="S29" s="27" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>-2792.8</v>
+        <v>-5062.5</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Capital Goods</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="D30" s="29" t="n">
-        <v>-52.4</v>
-      </c>
-      <c r="E30" s="29" t="n">
-        <v>-67.5</v>
-      </c>
-      <c r="F30" s="29" t="n">
-        <v>-24</v>
-      </c>
-      <c r="G30" s="30" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H30" s="30" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I30" s="29" t="n">
-        <v>-9.800000000000001</v>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="D30" s="27" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" s="29" t="n">
+        <v>-65</v>
+      </c>
+      <c r="H30" s="29" t="n">
+        <v>-25.8</v>
+      </c>
+      <c r="I30" s="27" t="n">
+        <v>17.2</v>
       </c>
       <c r="J30" s="29" t="n">
-        <v>-1404.8</v>
-      </c>
-      <c r="K30" s="29" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="L30" s="29" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="M30" s="28" t="n">
-        <v>-7.2</v>
+        <v>-1388.6</v>
+      </c>
+      <c r="K30" s="27" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="L30" s="27" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="M30" s="34" t="n">
+        <v>0.5</v>
       </c>
       <c r="N30" s="29" t="n">
-        <v>-28.3</v>
+        <v>-18.3</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>-53.4</v>
-      </c>
-      <c r="P30" s="30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Q30" s="27" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="R30" s="30" t="n">
-        <v>14.4</v>
+        <v>-81.09999999999999</v>
+      </c>
+      <c r="P30" s="27" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="Q30" s="29" t="n">
+        <v>-47.9</v>
+      </c>
+      <c r="R30" s="29" t="n">
+        <v>-22</v>
       </c>
       <c r="S30" s="27" t="n">
-        <v>19</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>-4822.4</v>
+        <v>-4835.4</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Diversified Commercial Services</t>
-        </is>
-      </c>
-      <c r="B31" s="31" t="n">
-        <v>3</v>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Asset Management Company</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="C31" s="29" t="n">
-        <v>-24.8</v>
+        <v>-16.3</v>
       </c>
       <c r="D31" s="29" t="n">
-        <v>-53.3</v>
+        <v>-20.6</v>
       </c>
       <c r="E31" s="29" t="n">
-        <v>-55.9</v>
+        <v>-89.5</v>
       </c>
       <c r="F31" s="29" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G31" s="30" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H31" s="30" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I31" s="29" t="n">
-        <v>-6.9</v>
+        <v>-65.40000000000001</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>63</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="I31" s="28" t="n">
+        <v>-1.9</v>
       </c>
       <c r="J31" s="29" t="n">
-        <v>-1523.6</v>
+        <v>-687.7</v>
       </c>
       <c r="K31" s="29" t="n">
-        <v>-17.4</v>
+        <v>-17.9</v>
       </c>
       <c r="L31" s="29" t="n">
-        <v>-14.1</v>
-      </c>
-      <c r="M31" s="29" t="n">
-        <v>-53.9</v>
+        <v>-7.4</v>
+      </c>
+      <c r="M31" s="28" t="n">
+        <v>-8</v>
       </c>
       <c r="N31" s="29" t="n">
-        <v>-46.3</v>
+        <v>-18.9</v>
       </c>
       <c r="O31" s="29" t="n">
-        <v>-54.9</v>
+        <v>-99.5</v>
       </c>
       <c r="P31" s="29" t="n">
-        <v>-683.4</v>
-      </c>
-      <c r="Q31" s="29" t="n">
-        <v>-863.4</v>
-      </c>
-      <c r="R31" s="29" t="n">
-        <v>-454.9</v>
-      </c>
-      <c r="S31" s="29" t="n">
-        <v>-854.9</v>
+        <v>-56.7</v>
+      </c>
+      <c r="Q31" s="27" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="R31" s="27" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="S31" s="27" t="n">
+        <v>22.4</v>
       </c>
       <c r="T31" s="29" t="n">
-        <v>-5706.4</v>
+        <v>-2531.5</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Construction Materials</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="n">
-        <v>2</v>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="n">
+        <v>11</v>
       </c>
       <c r="C32" s="29" t="n">
-        <v>-33.9</v>
+        <v>-23.5</v>
       </c>
       <c r="D32" s="29" t="n">
-        <v>-43.3</v>
+        <v>-54</v>
       </c>
       <c r="E32" s="29" t="n">
-        <v>-54.2</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="F32" s="29" t="n">
-        <v>-20.3</v>
+        <v>-31.7</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H32" s="27" t="n">
-        <v>15.2</v>
+        <v>12.9</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <v>14</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>-3.3</v>
+        <v>-10.1</v>
       </c>
       <c r="J32" s="29" t="n">
-        <v>-171.7</v>
+        <v>-1326.3</v>
       </c>
       <c r="K32" s="29" t="n">
-        <v>-11</v>
+        <v>-16.2</v>
       </c>
       <c r="L32" s="29" t="n">
-        <v>-5</v>
+        <v>-12.5</v>
       </c>
       <c r="M32" s="28" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N32" s="27" t="n">
-        <v>746.2</v>
-      </c>
-      <c r="O32" s="27" t="n">
-        <v>1479.6</v>
-      </c>
-      <c r="P32" s="27" t="n">
-        <v>770.1</v>
+        <v>-7.8</v>
+      </c>
+      <c r="N32" s="29" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="O32" s="29" t="n">
+        <v>-54.1</v>
+      </c>
+      <c r="P32" s="34" t="n">
+        <v>2.1</v>
       </c>
       <c r="Q32" s="27" t="n">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="R32" s="30" t="n">
-        <v>10</v>
+        <v>14.3</v>
       </c>
       <c r="S32" s="27" t="n">
-        <v>24</v>
+        <v>17.7</v>
       </c>
       <c r="T32" s="29" t="n">
-        <v>-103.3</v>
+        <v>-4561.1</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
-        <v>23</v>
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Diversified Commercial Services</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>3</v>
       </c>
       <c r="C33" s="29" t="n">
-        <v>-34.4</v>
-      </c>
-      <c r="D33" s="28" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="E33" s="30" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="F33" s="30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>34.1</v>
+        <v>-24.2</v>
+      </c>
+      <c r="D33" s="29" t="n">
+        <v>-54.9</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>-63.3</v>
+      </c>
+      <c r="F33" s="29" t="n">
+        <v>-37.7</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>11.8</v>
       </c>
       <c r="H33" s="30" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>317</v>
+        <v>-7.2</v>
+      </c>
+      <c r="J33" s="29" t="n">
+        <v>-1445.1</v>
       </c>
       <c r="K33" s="29" t="n">
-        <v>-20.9</v>
+        <v>-16.8</v>
       </c>
       <c r="L33" s="29" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="M33" s="30" t="n">
-        <v>9.4</v>
+        <v>-15.5</v>
+      </c>
+      <c r="M33" s="29" t="n">
+        <v>-54.5</v>
       </c>
       <c r="N33" s="29" t="n">
-        <v>-30.3</v>
+        <v>-46.8</v>
       </c>
       <c r="O33" s="29" t="n">
-        <v>-42.1</v>
-      </c>
-      <c r="P33" s="34" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q33" s="27" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="R33" s="27" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="S33" s="27" t="n">
-        <v>28.1</v>
+        <v>-55.6</v>
+      </c>
+      <c r="P33" s="29" t="n">
+        <v>-686.9</v>
+      </c>
+      <c r="Q33" s="29" t="n">
+        <v>-865.9</v>
+      </c>
+      <c r="R33" s="29" t="n">
+        <v>-455</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>-856.2</v>
       </c>
       <c r="T33" s="29" t="n">
-        <v>-149.4</v>
+        <v>-5445.1</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Consumer Services</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>2</v>
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="n">
+        <v>24</v>
       </c>
       <c r="C34" s="29" t="n">
-        <v>-36.7</v>
-      </c>
-      <c r="D34" s="29" t="n">
-        <v>-55.6</v>
-      </c>
-      <c r="E34" s="29" t="n">
-        <v>-75.8</v>
-      </c>
-      <c r="F34" s="29" t="n">
-        <v>-31.3</v>
+        <v>-32.2</v>
+      </c>
+      <c r="D34" s="28" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="E34" s="34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>2.7</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="H34" s="27" t="n">
-        <v>18.3</v>
+        <v>32.9</v>
+      </c>
+      <c r="H34" s="30" t="n">
+        <v>11.2</v>
       </c>
       <c r="I34" s="29" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="J34" s="29" t="n">
-        <v>-1379.6</v>
+        <v>-4.4</v>
+      </c>
+      <c r="J34" s="27" t="n">
+        <v>303.7</v>
       </c>
       <c r="K34" s="29" t="n">
-        <v>-18</v>
+        <v>-19.9</v>
       </c>
       <c r="L34" s="29" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="M34" s="29" t="n">
-        <v>-17.8</v>
+        <v>-14</v>
+      </c>
+      <c r="M34" s="30" t="n">
+        <v>7.6</v>
       </c>
       <c r="N34" s="29" t="n">
-        <v>-43.6</v>
+        <v>-30.1</v>
       </c>
       <c r="O34" s="29" t="n">
-        <v>-78.09999999999999</v>
-      </c>
-      <c r="P34" s="32" t="n">
-        <v>-13.5</v>
+        <v>-43.4</v>
+      </c>
+      <c r="P34" s="28" t="n">
+        <v>-2.4</v>
       </c>
       <c r="Q34" s="27" t="n">
-        <v>67.09999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="R34" s="27" t="n">
-        <v>27.3</v>
+        <v>40.4</v>
       </c>
       <c r="S34" s="27" t="n">
-        <v>16</v>
+        <v>26.5</v>
       </c>
       <c r="T34" s="29" t="n">
-        <v>-4717.4</v>
+        <v>-111.3</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Textiles</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="n">
-        <v>1</v>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="C35" s="29" t="n">
-        <v>-38.4</v>
-      </c>
-      <c r="D35" s="31" t="inlineStr"/>
-      <c r="E35" s="31" t="inlineStr"/>
-      <c r="F35" s="31" t="inlineStr"/>
-      <c r="G35" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="I35" s="30" t="n">
-        <v>0.3</v>
+        <v>-33.3</v>
+      </c>
+      <c r="D35" s="29" t="n">
+        <v>-44.9</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <v>-61.6</v>
+      </c>
+      <c r="F35" s="29" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G35" s="30" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I35" s="29" t="n">
+        <v>-3.6</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>-1533.5</v>
+        <v>-93.2</v>
       </c>
       <c r="K35" s="29" t="n">
-        <v>-13.6</v>
+        <v>-10.4</v>
       </c>
       <c r="L35" s="29" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="M35" s="29" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="N35" s="31" t="inlineStr"/>
-      <c r="O35" s="31" t="inlineStr"/>
-      <c r="P35" s="31" t="inlineStr"/>
+        <v>-6.4</v>
+      </c>
+      <c r="M35" s="28" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="N35" s="27" t="n">
+        <v>745.7</v>
+      </c>
+      <c r="O35" s="27" t="n">
+        <v>1478.9</v>
+      </c>
+      <c r="P35" s="27" t="n">
+        <v>766.6</v>
+      </c>
       <c r="Q35" s="27" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="R35" s="29" t="n">
-        <v>-16.3</v>
+        <v>39.2</v>
+      </c>
+      <c r="R35" s="30" t="n">
+        <v>9.9</v>
       </c>
       <c r="S35" s="27" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="T35" s="29" t="n">
-        <v>-5281.3</v>
+        <v>22.7</v>
+      </c>
+      <c r="T35" s="27" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>5</v>
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n">
+        <v>2</v>
       </c>
       <c r="C36" s="29" t="n">
-        <v>-39.8</v>
+        <v>-36.1</v>
       </c>
       <c r="D36" s="29" t="n">
-        <v>-47.2</v>
+        <v>-57.2</v>
       </c>
       <c r="E36" s="29" t="n">
-        <v>-52</v>
+        <v>-83.2</v>
       </c>
       <c r="F36" s="29" t="n">
-        <v>-19.6</v>
+        <v>-39</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H36" s="30" t="n">
-        <v>10</v>
+        <v>30.4</v>
+      </c>
+      <c r="H36" s="27" t="n">
+        <v>17.4</v>
       </c>
       <c r="I36" s="29" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J36" s="27" t="n">
-        <v>11896.6</v>
+        <v>-14.2</v>
+      </c>
+      <c r="J36" s="29" t="n">
+        <v>-1301.1</v>
       </c>
       <c r="K36" s="29" t="n">
         <v>-17.4</v>
       </c>
       <c r="L36" s="29" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="M36" s="32" t="n">
-        <v>-10.2</v>
+        <v>-11.9</v>
+      </c>
+      <c r="M36" s="29" t="n">
+        <v>-18.4</v>
       </c>
       <c r="N36" s="29" t="n">
-        <v>-30.7</v>
+        <v>-44.1</v>
       </c>
       <c r="O36" s="29" t="n">
-        <v>-59.4</v>
-      </c>
-      <c r="P36" s="28" t="n">
-        <v>-4</v>
+        <v>-78.8</v>
+      </c>
+      <c r="P36" s="29" t="n">
+        <v>-17</v>
       </c>
       <c r="Q36" s="27" t="n">
-        <v>48.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="R36" s="27" t="n">
-        <v>18.3</v>
+        <v>27.2</v>
       </c>
       <c r="S36" s="27" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T36" s="27" t="n">
-        <v>45785.8</v>
+        <v>14.7</v>
+      </c>
+      <c r="T36" s="29" t="n">
+        <v>-4456.1</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>Furniture, Home Furnishing</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="n">
-        <v>2</v>
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="C37" s="29" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="D37" s="29" t="n">
-        <v>-65.59999999999999</v>
-      </c>
-      <c r="E37" s="29" t="n">
-        <v>-69.2</v>
-      </c>
-      <c r="F37" s="29" t="n">
-        <v>-27.5</v>
-      </c>
-      <c r="G37" s="30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H37" s="27" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="I37" s="29" t="n">
-        <v>-4.8</v>
+        <v>-37.8</v>
+      </c>
+      <c r="D37" s="26" t="inlineStr"/>
+      <c r="E37" s="26" t="inlineStr"/>
+      <c r="F37" s="26" t="inlineStr"/>
+      <c r="G37" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="29" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="I37" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>-1468</v>
+        <v>-1455</v>
       </c>
       <c r="K37" s="29" t="n">
-        <v>-13.8</v>
+        <v>-13</v>
       </c>
       <c r="L37" s="29" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="M37" s="34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N37" s="29" t="n">
-        <v>-34.4</v>
-      </c>
-      <c r="O37" s="29" t="n">
-        <v>-63.2</v>
-      </c>
-      <c r="P37" s="28" t="n">
-        <v>-7.5</v>
-      </c>
+        <v>-6.2</v>
+      </c>
+      <c r="M37" s="29" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="N37" s="26" t="inlineStr"/>
+      <c r="O37" s="26" t="inlineStr"/>
+      <c r="P37" s="26" t="inlineStr"/>
       <c r="Q37" s="27" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="R37" s="27" t="n">
-        <v>28.9</v>
+        <v>30.2</v>
+      </c>
+      <c r="R37" s="29" t="n">
+        <v>-16.4</v>
       </c>
       <c r="S37" s="27" t="n">
-        <v>18.9</v>
+        <v>22.9</v>
       </c>
       <c r="T37" s="29" t="n">
-        <v>-5200</v>
+        <v>-5020</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Media, Entertainment &amp; Publication</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="n">
-        <v>10</v>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="C38" s="29" t="n">
-        <v>-57.6</v>
+        <v>-39.2</v>
       </c>
       <c r="D38" s="29" t="n">
-        <v>-66.40000000000001</v>
+        <v>-48.8</v>
       </c>
       <c r="E38" s="29" t="n">
-        <v>-78.40000000000001</v>
+        <v>-59.4</v>
       </c>
       <c r="F38" s="29" t="n">
-        <v>-59.8</v>
-      </c>
-      <c r="G38" s="29" t="n">
-        <v>-33.6</v>
-      </c>
-      <c r="H38" s="29" t="n">
-        <v>-18.4</v>
+        <v>-27.3</v>
+      </c>
+      <c r="G38" s="30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H38" s="30" t="n">
+        <v>9.1</v>
       </c>
       <c r="I38" s="29" t="n">
-        <v>-46</v>
-      </c>
-      <c r="J38" s="29" t="n">
-        <v>-1387.7</v>
+        <v>-3.7</v>
+      </c>
+      <c r="J38" s="27" t="n">
+        <v>11975.1</v>
       </c>
       <c r="K38" s="29" t="n">
-        <v>-61.2</v>
+        <v>-16.8</v>
       </c>
       <c r="L38" s="29" t="n">
-        <v>-33.9</v>
-      </c>
-      <c r="M38" s="29" t="n">
-        <v>-42.6</v>
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="M38" s="32" t="n">
+        <v>-10.8</v>
       </c>
       <c r="N38" s="29" t="n">
-        <v>-59.4</v>
+        <v>-31.2</v>
       </c>
       <c r="O38" s="29" t="n">
-        <v>-77.59999999999999</v>
-      </c>
-      <c r="P38" s="29" t="n">
-        <v>-18.5</v>
+        <v>-60.1</v>
+      </c>
+      <c r="P38" s="28" t="n">
+        <v>-7.5</v>
       </c>
       <c r="Q38" s="27" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="R38" s="34" t="n">
-        <v>2.3</v>
+        <v>45.9</v>
+      </c>
+      <c r="R38" s="27" t="n">
+        <v>18.2</v>
       </c>
       <c r="S38" s="27" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="T38" s="29" t="n">
-        <v>-4647.8</v>
+        <v>19.2</v>
+      </c>
+      <c r="T38" s="27" t="n">
+        <v>46047.1</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>Telecommunication</t>
-        </is>
-      </c>
-      <c r="B39" s="31" t="n">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Furniture, Home Furnishing</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="29" t="n">
-        <v>-124</v>
-      </c>
-      <c r="D39" s="31" t="inlineStr"/>
-      <c r="E39" s="31" t="inlineStr"/>
+        <v>-47.9</v>
+      </c>
+      <c r="D39" s="29" t="n">
+        <v>-67.2</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>-76.59999999999999</v>
+      </c>
       <c r="F39" s="29" t="n">
-        <v>-54.5</v>
-      </c>
-      <c r="G39" s="29" t="n">
-        <v>-48.8</v>
-      </c>
-      <c r="H39" s="29" t="n">
-        <v>-25.5</v>
+        <v>-35.2</v>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H39" s="27" t="n">
+        <v>16.2</v>
       </c>
       <c r="I39" s="29" t="n">
-        <v>-53.2</v>
+        <v>-5.1</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>-1397.9</v>
+        <v>-1389.5</v>
       </c>
       <c r="K39" s="29" t="n">
-        <v>-9.5</v>
+        <v>-13.2</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>-51.4</v>
-      </c>
-      <c r="M39" s="29" t="n">
-        <v>-112</v>
-      </c>
-      <c r="N39" s="31" t="inlineStr"/>
-      <c r="O39" s="31" t="inlineStr"/>
-      <c r="P39" s="29" t="n">
-        <v>-82</v>
-      </c>
-      <c r="Q39" s="29" t="n">
-        <v>-40.2</v>
-      </c>
-      <c r="R39" s="29" t="n">
-        <v>-81.3</v>
-      </c>
-      <c r="S39" s="29" t="n">
-        <v>-60.7</v>
+        <v>-8.9</v>
+      </c>
+      <c r="M39" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N39" s="29" t="n">
+        <v>-34.9</v>
+      </c>
+      <c r="O39" s="29" t="n">
+        <v>-63.9</v>
+      </c>
+      <c r="P39" s="32" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Q39" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="R39" s="27" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S39" s="27" t="n">
+        <v>17.6</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>-865.5</v>
+        <v>-4938.7</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Media, Entertainment &amp; Publication</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>-57</v>
+      </c>
+      <c r="D40" s="29" t="n">
+        <v>-68</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>-85.8</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>-67.5</v>
+      </c>
+      <c r="G40" s="29" t="n">
+        <v>-34.6</v>
+      </c>
+      <c r="H40" s="29" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="I40" s="29" t="n">
+        <v>-46.3</v>
+      </c>
+      <c r="J40" s="29" t="n">
+        <v>-1309.2</v>
+      </c>
+      <c r="K40" s="29" t="n">
+        <v>-60.6</v>
+      </c>
+      <c r="L40" s="29" t="n">
+        <v>-35.3</v>
+      </c>
+      <c r="M40" s="29" t="n">
+        <v>-43.2</v>
+      </c>
+      <c r="N40" s="29" t="n">
+        <v>-59.9</v>
+      </c>
+      <c r="O40" s="29" t="n">
+        <v>-78.3</v>
+      </c>
+      <c r="P40" s="29" t="n">
+        <v>-22</v>
+      </c>
+      <c r="Q40" s="27" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="R40" s="34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S40" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="T40" s="29" t="n">
+        <v>-4386.5</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>-123.4</v>
+      </c>
+      <c r="D41" s="26" t="inlineStr"/>
+      <c r="E41" s="26" t="inlineStr"/>
+      <c r="F41" s="29" t="n">
+        <v>-62.2</v>
+      </c>
+      <c r="G41" s="29" t="n">
+        <v>-49.8</v>
+      </c>
+      <c r="H41" s="29" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="I41" s="29" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="J41" s="29" t="n">
+        <v>-1319.4</v>
+      </c>
+      <c r="K41" s="29" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="L41" s="29" t="n">
+        <v>-52.8</v>
+      </c>
+      <c r="M41" s="29" t="n">
+        <v>-112.6</v>
+      </c>
+      <c r="N41" s="26" t="inlineStr"/>
+      <c r="O41" s="26" t="inlineStr"/>
+      <c r="P41" s="29" t="n">
+        <v>-85.5</v>
+      </c>
+      <c r="Q41" s="29" t="n">
+        <v>-42.7</v>
+      </c>
+      <c r="R41" s="29" t="n">
+        <v>-81.40000000000001</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>-62</v>
+      </c>
+      <c r="T41" s="29" t="n">
+        <v>-604.2</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Other Textile Products</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n">
+      <c r="B42" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="26" t="inlineStr"/>
-      <c r="D40" s="26" t="inlineStr"/>
-      <c r="E40" s="26" t="inlineStr"/>
-      <c r="F40" s="26" t="inlineStr"/>
-      <c r="G40" s="27" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="I40" s="26" t="inlineStr"/>
-      <c r="J40" s="29" t="n">
-        <v>-1521.6</v>
-      </c>
-      <c r="K40" s="26" t="inlineStr"/>
-      <c r="L40" s="26" t="inlineStr"/>
-      <c r="M40" s="26" t="inlineStr"/>
-      <c r="N40" s="26" t="inlineStr"/>
-      <c r="O40" s="26" t="inlineStr"/>
-      <c r="P40" s="26" t="inlineStr"/>
-      <c r="Q40" s="27" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="R40" s="30" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="S40" s="26" t="inlineStr"/>
-      <c r="T40" s="29" t="n">
-        <v>-5283.3</v>
+      <c r="C42" s="31" t="inlineStr"/>
+      <c r="D42" s="31" t="inlineStr"/>
+      <c r="E42" s="31" t="inlineStr"/>
+      <c r="F42" s="31" t="inlineStr"/>
+      <c r="G42" s="27" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="H42" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I42" s="31" t="inlineStr"/>
+      <c r="J42" s="29" t="n">
+        <v>-1443.1</v>
+      </c>
+      <c r="K42" s="31" t="inlineStr"/>
+      <c r="L42" s="31" t="inlineStr"/>
+      <c r="M42" s="31" t="inlineStr"/>
+      <c r="N42" s="31" t="inlineStr"/>
+      <c r="O42" s="31" t="inlineStr"/>
+      <c r="P42" s="31" t="inlineStr"/>
+      <c r="Q42" s="27" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="R42" s="30" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="S42" s="31" t="inlineStr"/>
+      <c r="T42" s="29" t="n">
+        <v>-5022</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Growth: &gt;=15% = dark green | 5–15% = light green | 0–5% = amber | −10–0% = light red | &lt;−10% = dark red  ||  Margin pp: &gt;=+2pp = dark green | 0–+2pp = light green | −2–0pp = light red | &lt;−2pp = dark red</t>
         </is>
@@ -3109,8 +3215,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A42:T42"/>
-    <mergeCell ref="A22:T22"/>
+    <mergeCell ref="A23:T23"/>
+    <mergeCell ref="A44:T44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10525,13 +10631,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA25"/>
+  <dimension ref="A1:BA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10591,6 +10697,497 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Result Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Industry Group</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Subsector</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Market Cap (Cr)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Screener Ticker</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Net Profit (Cr)</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>PAT Margin%</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Sales QoQ%</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA QoQ%</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>NP QoQ%</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>EPS QoQ%</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>PAT Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Sales YoY Q%</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA YoY Q%</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>NP YoY Q%</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>EPS YoY Q%</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Prev Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Prev Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Prev Qtr NP</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>Prev Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>LY Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>LY Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>LY Qtr NP</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>LY Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>FY Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>FY EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>FY NP (Cr)</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>FY EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>FY PAT Margin%</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>FY Sales YoY%</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>FY EBITDA YoY%</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>FY NP YoY%</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>FY EPS YoY%</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
+        <is>
+          <t>FY PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AX2" s="2" t="inlineStr">
+        <is>
+          <t>Prev FY Sales</t>
+        </is>
+      </c>
+      <c r="AY2" s="2" t="inlineStr">
+        <is>
+          <t>Prev FY EBITDA</t>
+        </is>
+      </c>
+      <c r="AZ2" s="2" t="inlineStr">
+        <is>
+          <t>Prev FY NP</t>
+        </is>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>Prev FY EPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Lloyds Luxuries</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LLOYDS</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="12" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W3" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="X3" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="12" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AC3" s="12" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>-14.55</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ3" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL3" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AM3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="3" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ3" s="3" t="n">
+        <v>-55.74</v>
+      </c>
+      <c r="AR3" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="12" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AW3" s="4" t="n">
+        <v>-40.52</v>
+      </c>
+      <c r="AX3" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AY3" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BA3" s="3" t="n">
+        <v>-2.79</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:BA3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:BA1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BA26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="16" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Financial Services</t>
         </is>
       </c>
@@ -11358,12 +11955,12 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Anand Rathi Wea.</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -11378,26 +11975,26 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Financial Products Distributor</t>
+          <t>Other Financial Services</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Nifty Smallcap 250, Nifty 500</t>
+          <t>Nifty Midcap 150, Nifty 500</t>
         </is>
       </c>
       <c r="G6" s="13" t="n">
-        <v>30153</v>
+        <v>31827</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>3632</v>
+        <v>4340</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>77</v>
+        <v>37.9</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -11406,141 +12003,141 @@
         </is>
       </c>
       <c r="L6" s="13" t="n">
-        <v>277</v>
+        <v>1058</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="N6" s="13" t="n">
-        <v>102</v>
+        <v>233</v>
       </c>
       <c r="O6" s="13" t="n">
-        <v>12.31</v>
+        <v>31.9</v>
       </c>
       <c r="P6" s="13" t="n">
-        <v>29.96</v>
+        <v>30.15</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>36.82</v>
+        <v>22.02</v>
       </c>
       <c r="R6" s="14" t="n">
-        <v>-0.7</v>
+        <v>-2.2</v>
       </c>
       <c r="S6" s="14" t="n">
-        <v>-36.2</v>
-      </c>
-      <c r="T6" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" s="35" t="n">
-        <v>2.4</v>
+        <v>-6.2</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>-3.4</v>
       </c>
       <c r="V6" s="14" t="n">
-        <v>-16.63</v>
-      </c>
-      <c r="W6" s="35" t="n">
-        <v>0.98</v>
+        <v>-1.27</v>
+      </c>
+      <c r="W6" s="14" t="n">
+        <v>-0.35</v>
       </c>
       <c r="X6" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y6" s="14" t="n">
-        <v>-6.7</v>
+        <v>30.1</v>
+      </c>
+      <c r="Y6" s="35" t="n">
+        <v>37.5</v>
       </c>
       <c r="Z6" s="35" t="n">
-        <v>41.7</v>
+        <v>45.6</v>
       </c>
       <c r="AA6" s="35" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="AB6" s="14" t="n">
-        <v>-11.82</v>
+        <v>45.9</v>
+      </c>
+      <c r="AB6" s="35" t="n">
+        <v>1.61</v>
       </c>
       <c r="AC6" s="35" t="n">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="AD6" s="13" t="n">
-        <v>279</v>
+        <v>1082</v>
       </c>
       <c r="AE6" s="13" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="AF6" s="13" t="n">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="AG6" s="13" t="n">
-        <v>12.02</v>
+        <v>33.02</v>
       </c>
       <c r="AH6" s="13" t="n">
-        <v>213</v>
+        <v>813</v>
       </c>
       <c r="AI6" s="13" t="n">
-        <v>89</v>
+        <v>232</v>
       </c>
       <c r="AJ6" s="13" t="n">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="AK6" s="13" t="n">
-        <v>8.720000000000001</v>
+        <v>21.86</v>
       </c>
       <c r="AL6" s="13" t="n">
-        <v>1107</v>
+        <v>3649</v>
       </c>
       <c r="AM6" s="13" t="n">
-        <v>472</v>
+        <v>1085</v>
       </c>
       <c r="AN6" s="13" t="n">
-        <v>391</v>
+        <v>766</v>
       </c>
       <c r="AO6" s="13" t="n">
-        <v>47.15</v>
+        <v>104.75</v>
       </c>
       <c r="AP6" s="13" t="n">
-        <v>42.64</v>
+        <v>29.73</v>
       </c>
       <c r="AQ6" s="13" t="n">
-        <v>35.32</v>
+        <v>20.99</v>
       </c>
       <c r="AR6" s="35" t="n">
-        <v>17.4</v>
+        <v>11.9</v>
       </c>
       <c r="AS6" s="35" t="n">
-        <v>10</v>
+        <v>19.1</v>
       </c>
       <c r="AT6" s="35" t="n">
-        <v>32.5</v>
+        <v>12</v>
       </c>
       <c r="AU6" s="35" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="AV6" s="14" t="n">
-        <v>-2.85</v>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="35" t="n">
+        <v>1.79</v>
       </c>
       <c r="AW6" s="35" t="n">
-        <v>4.04</v>
+        <v>0.01</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>943</v>
+        <v>3260</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>429</v>
+        <v>911</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>295</v>
+        <v>684</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>35.58</v>
+        <v>93.54000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Anand Rathi Shar</t>
+          <t>Anand Rathi Wea.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -11555,22 +12152,26 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Stockbroking &amp; Allied</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+          <t>Financial Products Distributor</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Smallcap 250, Nifty 500</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="n">
-        <v>3644</v>
+        <v>30153</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>581</v>
+        <v>3632</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>27.6</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -11579,141 +12180,141 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>6.69</v>
+        <v>12.31</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>43.53</v>
+        <v>29.96</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>16.47</v>
-      </c>
-      <c r="R7" s="12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S7" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>36.82</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>-36.2</v>
       </c>
       <c r="T7" s="12" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="U7" s="12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V7" s="12" t="n">
         <v>2.4</v>
       </c>
+      <c r="V7" s="4" t="n">
+        <v>-16.63</v>
+      </c>
       <c r="W7" s="12" t="n">
-        <v>1.15</v>
+        <v>0.98</v>
       </c>
       <c r="X7" s="12" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Y7" s="12" t="n">
-        <v>52.1</v>
+        <v>30</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>-6.7</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>121.1</v>
+        <v>41.7</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="AB7" s="12" t="n">
-        <v>6.85</v>
+        <v>41.2</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>-11.82</v>
       </c>
       <c r="AC7" s="12" t="n">
-        <v>6.92</v>
+        <v>3.02</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>6.04</v>
+        <v>12.02</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>4.2</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>931</v>
+        <v>1107</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>382</v>
+        <v>472</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>132</v>
+        <v>391</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>21.02</v>
+        <v>47.15</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>41.03</v>
+        <v>42.64</v>
       </c>
       <c r="AQ7" s="3" t="n">
-        <v>14.18</v>
+        <v>35.32</v>
       </c>
       <c r="AR7" s="12" t="n">
-        <v>10.3</v>
+        <v>17.4</v>
       </c>
       <c r="AS7" s="12" t="n">
-        <v>22.8</v>
+        <v>10</v>
       </c>
       <c r="AT7" s="12" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="AU7" s="4" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="AV7" s="12" t="n">
-        <v>4.18</v>
+        <v>32.5</v>
+      </c>
+      <c r="AU7" s="12" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AV7" s="4" t="n">
+        <v>-2.85</v>
       </c>
       <c r="AW7" s="12" t="n">
-        <v>1.86</v>
+        <v>4.04</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>844</v>
+        <v>943</v>
       </c>
       <c r="AY7" s="3" t="n">
-        <v>311</v>
+        <v>429</v>
       </c>
       <c r="AZ7" s="3" t="n">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="BA7" s="3" t="n">
-        <v>23.41</v>
+        <v>35.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>HDFC AMC</t>
+          <t>Anand Rathi Shar</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -11728,26 +12329,22 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Asset Management Company</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Nifty 500</t>
-        </is>
-      </c>
+          <t>Stockbroking &amp; Allied</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="13" t="n">
-        <v>114049</v>
+        <v>3644</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>2662</v>
+        <v>581</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>39.9</v>
+        <v>27.6</v>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -11756,141 +12353,141 @@
         </is>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1050</v>
+        <v>255</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>846</v>
+        <v>111</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>623</v>
+        <v>42</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>14.55</v>
+        <v>6.69</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>80.56999999999999</v>
+        <v>43.53</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="R8" s="14" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="S8" s="14" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="T8" s="14" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="U8" s="14" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="V8" s="14" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="W8" s="14" t="n">
-        <v>-12.36</v>
+        <v>16.47</v>
+      </c>
+      <c r="R8" s="35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S8" s="35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="T8" s="35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U8" s="35" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V8" s="35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W8" s="35" t="n">
+        <v>1.15</v>
       </c>
       <c r="X8" s="35" t="n">
-        <v>16.5</v>
+        <v>28.1</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="Z8" s="14" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA8" s="14" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="AB8" s="14" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="AC8" s="14" t="n">
-        <v>-11.59</v>
+        <v>52.1</v>
+      </c>
+      <c r="Z8" s="35" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="AA8" s="35" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AB8" s="35" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AC8" s="35" t="n">
+        <v>6.92</v>
       </c>
       <c r="AD8" s="13" t="n">
-        <v>1074</v>
+        <v>248</v>
       </c>
       <c r="AE8" s="13" t="n">
-        <v>877</v>
+        <v>102</v>
       </c>
       <c r="AF8" s="13" t="n">
-        <v>770</v>
+        <v>38</v>
       </c>
       <c r="AG8" s="13" t="n">
-        <v>17.98</v>
+        <v>6.04</v>
       </c>
       <c r="AH8" s="13" t="n">
-        <v>901</v>
+        <v>199</v>
       </c>
       <c r="AI8" s="13" t="n">
-        <v>731</v>
+        <v>73</v>
       </c>
       <c r="AJ8" s="13" t="n">
-        <v>639</v>
+        <v>19</v>
       </c>
       <c r="AK8" s="13" t="n">
-        <v>14.94</v>
+        <v>4.2</v>
       </c>
       <c r="AL8" s="13" t="n">
-        <v>4119</v>
+        <v>931</v>
       </c>
       <c r="AM8" s="13" t="n">
-        <v>3297</v>
+        <v>382</v>
       </c>
       <c r="AN8" s="13" t="n">
-        <v>2859</v>
+        <v>132</v>
       </c>
       <c r="AO8" s="13" t="n">
-        <v>66.75</v>
+        <v>21.02</v>
       </c>
       <c r="AP8" s="13" t="n">
-        <v>80.04000000000001</v>
+        <v>41.03</v>
       </c>
       <c r="AQ8" s="13" t="n">
-        <v>69.41</v>
+        <v>14.18</v>
       </c>
       <c r="AR8" s="35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS8" s="14" t="n">
-        <v>-1.5</v>
+        <v>10.3</v>
+      </c>
+      <c r="AS8" s="35" t="n">
+        <v>22.8</v>
       </c>
       <c r="AT8" s="35" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="AU8" s="35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AV8" s="14" t="n">
-        <v>-2.58</v>
+        <v>26.9</v>
+      </c>
+      <c r="AU8" s="14" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="AV8" s="35" t="n">
+        <v>4.18</v>
       </c>
       <c r="AW8" s="35" t="n">
-        <v>8.640000000000001</v>
+        <v>1.86</v>
       </c>
       <c r="AX8" s="13" t="n">
-        <v>4050</v>
+        <v>844</v>
       </c>
       <c r="AY8" s="13" t="n">
-        <v>3346</v>
+        <v>311</v>
       </c>
       <c r="AZ8" s="13" t="n">
-        <v>2461</v>
+        <v>104</v>
       </c>
       <c r="BA8" s="13" t="n">
-        <v>57.55</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ICICI Lombard</t>
+          <t>HDFC AMC</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11905,26 +12502,26 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>General Insurance</t>
+          <t>Asset Management Company</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty 500</t>
+          <t>Nifty 500</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>93960</v>
+        <v>114049</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1886</v>
+        <v>2662</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>33.9</v>
+        <v>39.9</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -11933,130 +12530,130 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6825</v>
+        <v>1050</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>686</v>
+        <v>846</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>547</v>
+        <v>623</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>10.96</v>
+        <v>14.55</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>10.05</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>8.01</v>
+        <v>59.33</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-1.2</v>
+        <v>-2.2</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-19.7</v>
+        <v>-3.5</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-17</v>
+        <v>-19.1</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-17.2</v>
+        <v>-19.1</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-2.32</v>
+        <v>-1.09</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.53</v>
+        <v>-12.36</v>
       </c>
       <c r="X9" s="12" t="n">
-        <v>12.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Z9" s="12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA9" s="12" t="n">
-        <v>6.6</v>
+        <v>15.7</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>-2.6</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>-0.42</v>
+        <v>-11.59</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>6905</v>
+        <v>1074</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>854</v>
+        <v>877</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>659</v>
+        <v>770</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>13.23</v>
+        <v>17.98</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>6051</v>
+        <v>901</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>609</v>
+        <v>731</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>510</v>
+        <v>639</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>10.28</v>
+        <v>14.94</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>26994</v>
+        <v>4119</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>3565</v>
+        <v>3297</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>2772</v>
+        <v>2859</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>55.61</v>
+        <v>66.75</v>
       </c>
       <c r="AP9" s="3" t="n">
-        <v>13.21</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="AQ9" s="3" t="n">
-        <v>10.27</v>
+        <v>69.41</v>
       </c>
       <c r="AR9" s="12" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AS9" s="12" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
+      </c>
+      <c r="AS9" s="4" t="n">
+        <v>-1.5</v>
       </c>
       <c r="AT9" s="12" t="n">
-        <v>10.5</v>
+        <v>16.2</v>
       </c>
       <c r="AU9" s="12" t="n">
-        <v>9.9</v>
+        <v>16</v>
       </c>
       <c r="AV9" s="4" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="AW9" s="4" t="n">
-        <v>-0.2</v>
+        <v>-2.58</v>
+      </c>
+      <c r="AW9" s="12" t="n">
+        <v>8.640000000000001</v>
       </c>
       <c r="AX9" s="3" t="n">
-        <v>23961</v>
+        <v>4050</v>
       </c>
       <c r="AY9" s="3" t="n">
-        <v>3407</v>
+        <v>3346</v>
       </c>
       <c r="AZ9" s="3" t="n">
-        <v>2508</v>
+        <v>2461</v>
       </c>
       <c r="BA9" s="3" t="n">
-        <v>50.6</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="10">
@@ -12085,148 +12682,156 @@
           <t>General Insurance</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n">
-        <v>94511</v>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1896</v>
+        <v>93960</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr"/>
+        <v>1886</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>33.9</v>
+      </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="L10" s="13" t="n">
         <v>6825</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="M10" s="13" t="n">
         <v>686</v>
       </c>
-      <c r="M10" s="13" t="n">
-        <v>718</v>
-      </c>
       <c r="N10" s="13" t="n">
-        <v>14.41</v>
+        <v>547</v>
       </c>
       <c r="O10" s="13" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="P10" s="13" t="n">
         <v>10.05</v>
       </c>
-      <c r="P10" s="13" t="n">
-        <v>10.52</v>
-      </c>
       <c r="Q10" s="13" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="R10" s="14" t="n">
         <v>-1.2</v>
       </c>
-      <c r="R10" s="14" t="n">
+      <c r="S10" s="14" t="n">
         <v>-19.7</v>
       </c>
-      <c r="S10" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" s="35" t="n">
-        <v>8.9</v>
+      <c r="T10" s="14" t="n">
+        <v>-17</v>
       </c>
       <c r="U10" s="14" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="V10" s="14" t="n">
         <v>-2.32</v>
       </c>
-      <c r="V10" s="35" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="W10" s="35" t="n">
+      <c r="W10" s="14" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="X10" s="35" t="n">
         <v>12.8</v>
       </c>
-      <c r="X10" s="35" t="n">
+      <c r="Y10" s="35" t="n">
         <v>12.6</v>
       </c>
-      <c r="Y10" s="35" t="n">
-        <v>40.8</v>
-      </c>
       <c r="Z10" s="35" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="AA10" s="14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA10" s="35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AB10" s="14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AB10" s="35" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC10" s="35" t="n">
+      <c r="AC10" s="14" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="AD10" s="13" t="n">
         <v>6905</v>
       </c>
-      <c r="AD10" s="13" t="n">
+      <c r="AE10" s="13" t="n">
         <v>854</v>
       </c>
-      <c r="AE10" s="13" t="n">
+      <c r="AF10" s="13" t="n">
         <v>659</v>
       </c>
-      <c r="AF10" s="13" t="n">
+      <c r="AG10" s="13" t="n">
         <v>13.23</v>
       </c>
-      <c r="AG10" s="13" t="n">
+      <c r="AH10" s="13" t="n">
         <v>6051</v>
       </c>
-      <c r="AH10" s="13" t="n">
+      <c r="AI10" s="13" t="n">
         <v>609</v>
       </c>
-      <c r="AI10" s="13" t="n">
+      <c r="AJ10" s="13" t="n">
         <v>510</v>
       </c>
-      <c r="AJ10" s="13" t="n">
+      <c r="AK10" s="13" t="n">
         <v>10.28</v>
       </c>
-      <c r="AK10" s="13" t="n">
+      <c r="AL10" s="13" t="n">
         <v>26994</v>
       </c>
-      <c r="AL10" s="13" t="n">
+      <c r="AM10" s="13" t="n">
         <v>3565</v>
       </c>
-      <c r="AM10" s="13" t="n">
-        <v>3659</v>
-      </c>
       <c r="AN10" s="13" t="n">
-        <v>73.40000000000001</v>
+        <v>2772</v>
       </c>
       <c r="AO10" s="13" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="AP10" s="13" t="n">
         <v>13.21</v>
       </c>
-      <c r="AP10" s="13" t="n">
-        <v>13.55</v>
-      </c>
       <c r="AQ10" s="13" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="AR10" s="35" t="n">
         <v>12.7</v>
       </c>
-      <c r="AR10" s="35" t="n">
+      <c r="AS10" s="35" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS10" s="35" t="n">
-        <v>45.9</v>
-      </c>
       <c r="AT10" s="35" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="AU10" s="14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU10" s="35" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AV10" s="14" t="n">
         <v>-1.01</v>
       </c>
-      <c r="AV10" s="35" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AW10" s="35" t="n">
+      <c r="AW10" s="14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AX10" s="13" t="n">
         <v>23961</v>
       </c>
-      <c r="AX10" s="13" t="n">
+      <c r="AY10" s="13" t="n">
         <v>3407</v>
       </c>
-      <c r="AY10" s="13" t="n">
+      <c r="AZ10" s="13" t="n">
         <v>2508</v>
       </c>
-      <c r="AZ10" s="13" t="n">
+      <c r="BA10" s="13" t="n">
         <v>50.6</v>
       </c>
-      <c r="BA10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -12236,7 +12841,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>HDB FINANC SER</t>
+          <t>ICICI Lombard</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -12251,143 +12856,161 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Non Banking Financial Company (NBFC)</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Midcap 150, Nifty 500</t>
-        </is>
+          <t>General Insurance</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>94511</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>57409</v>
+        <v>1896</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>691</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>22.6</v>
-      </c>
+        <v>25.9</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>HDBFS</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
           <t>Mar 2026</t>
         </is>
       </c>
+      <c r="K11" s="3" t="n">
+        <v>6825</v>
+      </c>
       <c r="L11" s="3" t="n">
-        <v>4745</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
+        <v>686</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>718</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>751</v>
+        <v>14.41</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
+        <v>10.05</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>10.52</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="R11" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S11" s="3" t="inlineStr"/>
+        <v>-1.2</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <v>9</v>
+      </c>
       <c r="T11" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U11" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="V11" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>0.98</v>
+      </c>
       <c r="W11" s="12" t="n">
-        <v>2.05</v>
+        <v>12.8</v>
       </c>
       <c r="X11" s="12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Y11" s="3" t="inlineStr"/>
+        <v>12.6</v>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>40.8</v>
+      </c>
       <c r="Z11" s="12" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="AA11" s="12" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="AB11" s="3" t="inlineStr"/>
+        <v>40.2</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>2.09</v>
+      </c>
       <c r="AC11" s="12" t="n">
-        <v>3.38</v>
+        <v>6905</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>4674</v>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
+        <v>854</v>
+      </c>
+      <c r="AE11" s="3" t="n">
+        <v>659</v>
+      </c>
       <c r="AF11" s="3" t="n">
-        <v>644</v>
+        <v>13.23</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>7.76</v>
+        <v>6051</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>4266</v>
-      </c>
-      <c r="AI11" s="3" t="inlineStr"/>
+        <v>609</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>510</v>
+      </c>
       <c r="AJ11" s="3" t="n">
-        <v>531</v>
+        <v>10.28</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>6.67</v>
+        <v>26994</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>18430</v>
-      </c>
-      <c r="AM11" s="3" t="inlineStr"/>
+        <v>3565</v>
+      </c>
+      <c r="AM11" s="3" t="n">
+        <v>3659</v>
+      </c>
       <c r="AN11" s="3" t="n">
-        <v>2544</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>30.64</v>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
+        <v>13.21</v>
+      </c>
+      <c r="AP11" s="3" t="n">
+        <v>13.55</v>
+      </c>
       <c r="AQ11" s="3" t="n">
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
       <c r="AR11" s="12" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AS11" s="3" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="AS11" s="12" t="n">
+        <v>45.9</v>
+      </c>
       <c r="AT11" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AU11" s="12" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AV11" s="3" t="inlineStr"/>
+        <v>45.1</v>
+      </c>
+      <c r="AU11" s="4" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="AV11" s="12" t="n">
+        <v>3.08</v>
+      </c>
       <c r="AW11" s="12" t="n">
-        <v>0.45</v>
+        <v>23961</v>
       </c>
       <c r="AX11" s="3" t="n">
-        <v>16300</v>
-      </c>
-      <c r="AY11" s="3" t="inlineStr"/>
+        <v>3407</v>
+      </c>
+      <c r="AY11" s="3" t="n">
+        <v>2508</v>
+      </c>
       <c r="AZ11" s="3" t="n">
-        <v>2176</v>
-      </c>
-      <c r="BA11" s="3" t="n">
-        <v>27.34</v>
-      </c>
+        <v>50.6</v>
+      </c>
+      <c r="BA11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Anand Rathi Wea.</t>
+          <t>HDB FINANC SER</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -12402,161 +13025,143 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Financial Products Distributor</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>30251</v>
+          <t>Non Banking Financial Company (NBFC)</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
       </c>
       <c r="G12" s="13" t="n">
-        <v>3644</v>
+        <v>57409</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr"/>
+        <v>691</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>22.6</v>
+      </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
+          <t>HDBFS</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="K12" s="13" t="n">
-        <v>277</v>
-      </c>
       <c r="L12" s="13" t="n">
-        <v>83</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>102</v>
-      </c>
+        <v>4745</v>
+      </c>
+      <c r="M12" s="13" t="inlineStr"/>
       <c r="N12" s="13" t="n">
-        <v>12.31</v>
+        <v>751</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="P12" s="13" t="n">
-        <v>36.82</v>
-      </c>
+        <v>9.039999999999999</v>
+      </c>
+      <c r="P12" s="13" t="inlineStr"/>
       <c r="Q12" s="13" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="R12" s="14" t="n">
-        <v>-36.2</v>
-      </c>
-      <c r="S12" s="35" t="n">
-        <v>2</v>
-      </c>
+        <v>15.83</v>
+      </c>
+      <c r="R12" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" s="13" t="inlineStr"/>
       <c r="T12" s="35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" s="14" t="n">
-        <v>-16.63</v>
-      </c>
-      <c r="V12" s="35" t="n">
-        <v>0.98</v>
-      </c>
+        <v>16.6</v>
+      </c>
+      <c r="U12" s="35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V12" s="13" t="inlineStr"/>
       <c r="W12" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="X12" s="14" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="Y12" s="35" t="n">
-        <v>41.7</v>
-      </c>
+        <v>2.05</v>
+      </c>
+      <c r="X12" s="35" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Y12" s="13" t="inlineStr"/>
       <c r="Z12" s="35" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="AA12" s="14" t="n">
-        <v>-11.82</v>
-      </c>
-      <c r="AB12" s="35" t="n">
-        <v>3.02</v>
-      </c>
+        <v>41.4</v>
+      </c>
+      <c r="AA12" s="35" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="AB12" s="13" t="inlineStr"/>
       <c r="AC12" s="35" t="n">
-        <v>279</v>
+        <v>3.38</v>
       </c>
       <c r="AD12" s="13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AE12" s="13" t="n">
-        <v>100</v>
-      </c>
+        <v>4674</v>
+      </c>
+      <c r="AE12" s="13" t="inlineStr"/>
       <c r="AF12" s="13" t="n">
-        <v>12.02</v>
+        <v>644</v>
       </c>
       <c r="AG12" s="13" t="n">
-        <v>213</v>
+        <v>7.76</v>
       </c>
       <c r="AH12" s="13" t="n">
-        <v>89</v>
-      </c>
-      <c r="AI12" s="13" t="n">
-        <v>72</v>
-      </c>
+        <v>4266</v>
+      </c>
+      <c r="AI12" s="13" t="inlineStr"/>
       <c r="AJ12" s="13" t="n">
-        <v>8.720000000000001</v>
+        <v>531</v>
       </c>
       <c r="AK12" s="13" t="n">
-        <v>1107</v>
+        <v>6.67</v>
       </c>
       <c r="AL12" s="13" t="n">
-        <v>472</v>
-      </c>
-      <c r="AM12" s="13" t="n">
-        <v>391</v>
-      </c>
+        <v>18430</v>
+      </c>
+      <c r="AM12" s="13" t="inlineStr"/>
       <c r="AN12" s="13" t="n">
-        <v>47.15</v>
+        <v>2544</v>
       </c>
       <c r="AO12" s="13" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="AP12" s="13" t="n">
-        <v>35.32</v>
-      </c>
+        <v>30.64</v>
+      </c>
+      <c r="AP12" s="13" t="inlineStr"/>
       <c r="AQ12" s="13" t="n">
-        <v>17.4</v>
+        <v>13.8</v>
       </c>
       <c r="AR12" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS12" s="35" t="n">
-        <v>32.5</v>
-      </c>
+        <v>13.1</v>
+      </c>
+      <c r="AS12" s="13" t="inlineStr"/>
       <c r="AT12" s="35" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="AU12" s="14" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="AV12" s="35" t="n">
-        <v>4.04</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="AU12" s="35" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AV12" s="13" t="inlineStr"/>
       <c r="AW12" s="35" t="n">
-        <v>943</v>
+        <v>0.45</v>
       </c>
       <c r="AX12" s="13" t="n">
-        <v>429</v>
-      </c>
-      <c r="AY12" s="13" t="n">
-        <v>295</v>
-      </c>
+        <v>16300</v>
+      </c>
+      <c r="AY12" s="13" t="inlineStr"/>
       <c r="AZ12" s="13" t="n">
-        <v>35.58</v>
-      </c>
-      <c r="BA12" s="13" t="inlineStr"/>
+        <v>2176</v>
+      </c>
+      <c r="BA12" s="13" t="n">
+        <v>27.34</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>HDFC Life Insur.</t>
+          <t>Anand Rathi Wea.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -12571,169 +13176,161 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Nifty 50, Nifty 500</t>
-        </is>
+          <t>Financial Products Distributor</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>30251</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>136266</v>
+        <v>3644</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>632</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>71.3</v>
-      </c>
+        <v>77.3</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
           <t>Mar 2026</t>
         </is>
       </c>
+      <c r="K13" s="3" t="n">
+        <v>277</v>
+      </c>
       <c r="L13" s="3" t="n">
-        <v>19890</v>
+        <v>83</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>497</v>
+        <v>12.31</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>2.31</v>
+        <v>29.96</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.54</v>
+        <v>36.82</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2.5</v>
+        <v>-0.7</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-32.4</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>-60.1</v>
+        <v>-36.2</v>
+      </c>
+      <c r="S13" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="T13" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="U13" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>-0.38</v>
+        <v>2.4</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>-16.63</v>
+      </c>
+      <c r="V13" s="12" t="n">
+        <v>0.98</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>1.08</v>
+        <v>30</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="Y13" s="4" t="n">
-        <v>-71.40000000000001</v>
+        <v>-6.7</v>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>41.7</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA13" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB13" s="4" t="n">
-        <v>-1.02</v>
+        <v>41.2</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="AB13" s="12" t="n">
+        <v>3.02</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>0.54</v>
+        <v>279</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>29428</v>
+        <v>130</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>418</v>
+        <v>12.02</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>1.94</v>
+        <v>213</v>
       </c>
       <c r="AH13" s="3" t="n">
-        <v>24191</v>
+        <v>89</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>377</v>
+        <v>72</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>475</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>2.21</v>
+        <v>1107</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>99432</v>
+        <v>472</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>1133</v>
+        <v>391</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>1912</v>
+        <v>47.15</v>
       </c>
       <c r="AO13" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>42.64</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>1.14</v>
+        <v>35.32</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>1.92</v>
+        <v>17.4</v>
       </c>
       <c r="AR13" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AS13" s="12" t="n">
-        <v>10.2</v>
+        <v>32.5</v>
       </c>
       <c r="AT13" s="12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU13" s="12" t="n">
-        <v>5.4</v>
+        <v>32.5</v>
+      </c>
+      <c r="AU13" s="4" t="n">
+        <v>-2.85</v>
       </c>
       <c r="AV13" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AW13" s="4" t="n">
-        <v>-0.03</v>
+        <v>4.04</v>
+      </c>
+      <c r="AW13" s="12" t="n">
+        <v>943</v>
       </c>
       <c r="AX13" s="3" t="n">
-        <v>92922</v>
+        <v>429</v>
       </c>
       <c r="AY13" s="3" t="n">
-        <v>1028</v>
+        <v>295</v>
       </c>
       <c r="AZ13" s="3" t="n">
-        <v>1811</v>
-      </c>
-      <c r="BA13" s="3" t="n">
-        <v>8.41</v>
-      </c>
+        <v>35.58</v>
+      </c>
+      <c r="BA13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>ICICI Pru Life</t>
+          <t>HDFC Life Insur.</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -12753,21 +13350,21 @@
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Nifty Midcap 150, Nifty 500</t>
+          <t>Nifty 50, Nifty 500</t>
         </is>
       </c>
       <c r="G14" s="13" t="n">
-        <v>81179</v>
+        <v>136266</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>560</v>
+        <v>632</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>50.5</v>
+        <v>71.3</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -12776,137 +13373,141 @@
         </is>
       </c>
       <c r="L14" s="13" t="n">
-        <v>3185</v>
+        <v>19890</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>-754</v>
+        <v>108</v>
       </c>
       <c r="N14" s="13" t="n">
-        <v>624</v>
+        <v>497</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>4.3</v>
+        <v>2.31</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>-23.67</v>
+        <v>0.54</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>19.59</v>
+        <v>2.5</v>
       </c>
       <c r="R14" s="14" t="n">
-        <v>-86.09999999999999</v>
-      </c>
-      <c r="S14" s="13" t="inlineStr"/>
+        <v>-32.4</v>
+      </c>
+      <c r="S14" s="14" t="n">
+        <v>-60.1</v>
+      </c>
       <c r="T14" s="35" t="n">
-        <v>61.2</v>
+        <v>18.9</v>
       </c>
       <c r="U14" s="35" t="n">
-        <v>61</v>
+        <v>19.1</v>
       </c>
       <c r="V14" s="14" t="n">
-        <v>-26.92</v>
+        <v>-0.38</v>
       </c>
       <c r="W14" s="35" t="n">
-        <v>17.9</v>
+        <v>1.08</v>
       </c>
       <c r="X14" s="14" t="n">
-        <v>-79.7</v>
-      </c>
-      <c r="Y14" s="13" t="inlineStr"/>
+        <v>-17.8</v>
+      </c>
+      <c r="Y14" s="14" t="n">
+        <v>-71.40000000000001</v>
+      </c>
       <c r="Z14" s="35" t="n">
-        <v>62.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA14" s="35" t="n">
-        <v>61</v>
+        <v>4.5</v>
       </c>
       <c r="AB14" s="14" t="n">
-        <v>-26.32</v>
+        <v>-1.02</v>
       </c>
       <c r="AC14" s="35" t="n">
-        <v>17.14</v>
+        <v>0.54</v>
       </c>
       <c r="AD14" s="13" t="n">
-        <v>22834</v>
+        <v>29428</v>
       </c>
       <c r="AE14" s="13" t="n">
-        <v>741</v>
+        <v>271</v>
       </c>
       <c r="AF14" s="13" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="AG14" s="13" t="n">
-        <v>2.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH14" s="13" t="n">
-        <v>15687</v>
+        <v>24191</v>
       </c>
       <c r="AI14" s="13" t="n">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="AJ14" s="13" t="n">
-        <v>385</v>
+        <v>475</v>
       </c>
       <c r="AK14" s="13" t="n">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="AL14" s="13" t="n">
-        <v>63357</v>
+        <v>99432</v>
       </c>
       <c r="AM14" s="13" t="n">
-        <v>181</v>
+        <v>1133</v>
       </c>
       <c r="AN14" s="13" t="n">
-        <v>1608</v>
+        <v>1912</v>
       </c>
       <c r="AO14" s="13" t="n">
-        <v>11.09</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AP14" s="13" t="n">
-        <v>0.29</v>
+        <v>1.14</v>
       </c>
       <c r="AQ14" s="13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AR14" s="14" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AS14" s="14" t="n">
-        <v>-84.40000000000001</v>
+        <v>1.92</v>
+      </c>
+      <c r="AR14" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS14" s="35" t="n">
+        <v>10.2</v>
       </c>
       <c r="AT14" s="35" t="n">
-        <v>35.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU14" s="35" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="AV14" s="14" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="AW14" s="35" t="n">
-        <v>0.86</v>
+        <v>5.4</v>
+      </c>
+      <c r="AV14" s="35" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AW14" s="14" t="n">
+        <v>-0.03</v>
       </c>
       <c r="AX14" s="13" t="n">
-        <v>70778</v>
+        <v>92922</v>
       </c>
       <c r="AY14" s="13" t="n">
-        <v>1157</v>
+        <v>1028</v>
       </c>
       <c r="AZ14" s="13" t="n">
-        <v>1186</v>
+        <v>1811</v>
       </c>
       <c r="BA14" s="13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>16 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Roselabs Finance</t>
+          <t>ICICI Pru Life</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -12921,20 +13522,26 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Other Financial Services</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr"/>
+          <t>Life Insurance</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>23.5</v>
+        <v>81179</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>560</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>50.5</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>531324</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -12943,111 +13550,137 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>3185</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-0.05</v>
+        <v>-754</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-0.16</v>
+        <v>624</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
+        <v>4.3</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>-23.67</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>19.59</v>
+      </c>
       <c r="R15" s="4" t="n">
-        <v>-100</v>
+        <v>-86.09999999999999</v>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr"/>
+      <c r="T15" s="12" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="U15" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>-26.92</v>
+      </c>
+      <c r="W15" s="12" t="n">
+        <v>17.9</v>
+      </c>
       <c r="X15" s="4" t="n">
-        <v>-100</v>
+        <v>-79.7</v>
       </c>
       <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="Z15" s="12" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="AA15" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>-26.32</v>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>17.14</v>
+      </c>
       <c r="AD15" s="3" t="n">
-        <v>1.21</v>
+        <v>22834</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>-0.04</v>
+        <v>741</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>-0.04</v>
+        <v>387</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>-0.04</v>
+        <v>2.67</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>0.71</v>
+        <v>15687</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>-0.05</v>
+        <v>415</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>-0.05</v>
+        <v>385</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>-0.05</v>
+        <v>2.67</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>1.21</v>
+        <v>63357</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>-0.2</v>
+        <v>181</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.31</v>
+        <v>1608</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>-0.31</v>
+        <v>11.09</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>-16.53</v>
+        <v>0.29</v>
       </c>
       <c r="AQ15" s="3" t="n">
-        <v>-25.62</v>
-      </c>
-      <c r="AR15" s="12" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="12" t="n">
-        <v>27.13</v>
+        <v>2.54</v>
+      </c>
+      <c r="AR15" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AS15" s="4" t="n">
+        <v>-84.40000000000001</v>
+      </c>
+      <c r="AT15" s="12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="AU15" s="12" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="AV15" s="4" t="n">
+        <v>-1.34</v>
       </c>
       <c r="AW15" s="12" t="n">
-        <v>15.23</v>
+        <v>0.86</v>
       </c>
       <c r="AX15" s="3" t="n">
-        <v>0.71</v>
+        <v>70778</v>
       </c>
       <c r="AY15" s="3" t="n">
-        <v>-0.31</v>
+        <v>1157</v>
       </c>
       <c r="AZ15" s="3" t="n">
-        <v>-0.29</v>
+        <v>1186</v>
       </c>
       <c r="BA15" s="3" t="n">
-        <v>-0.29</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>16 Apr 2026</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>HDB FINANC SER</t>
+          <t>Roselabs Finance</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -13062,135 +13695,133 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Non Banking Financial Company (NBFC)</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>57662</v>
-      </c>
+          <t>Other Financial Services</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr"/>
       <c r="G16" s="13" t="n">
-        <v>694</v>
+        <v>23.5</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="I16" s="13" t="inlineStr"/>
       <c r="J16" s="13" t="inlineStr">
         <is>
+          <t>531324</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="K16" s="13" t="n">
-        <v>4745</v>
-      </c>
-      <c r="L16" s="13" t="inlineStr"/>
+      <c r="L16" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" s="13" t="n">
-        <v>751</v>
+        <v>-0.05</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="O16" s="13" t="inlineStr"/>
-      <c r="P16" s="13" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="Q16" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R16" s="13" t="inlineStr"/>
-      <c r="S16" s="35" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T16" s="35" t="n">
-        <v>16.5</v>
-      </c>
+        <v>-0.16</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="P16" s="13" t="inlineStr"/>
+      <c r="Q16" s="13" t="inlineStr"/>
+      <c r="R16" s="14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="S16" s="13" t="inlineStr"/>
+      <c r="T16" s="13" t="inlineStr"/>
       <c r="U16" s="13" t="inlineStr"/>
-      <c r="V16" s="35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W16" s="35" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="X16" s="13" t="inlineStr"/>
-      <c r="Y16" s="35" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Z16" s="35" t="n">
-        <v>35.5</v>
-      </c>
+      <c r="V16" s="13" t="inlineStr"/>
+      <c r="W16" s="13" t="inlineStr"/>
+      <c r="X16" s="14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="Y16" s="13" t="inlineStr"/>
+      <c r="Z16" s="13" t="inlineStr"/>
       <c r="AA16" s="13" t="inlineStr"/>
-      <c r="AB16" s="35" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AC16" s="35" t="n">
-        <v>4674</v>
-      </c>
-      <c r="AD16" s="13" t="inlineStr"/>
+      <c r="AB16" s="13" t="inlineStr"/>
+      <c r="AC16" s="13" t="inlineStr"/>
+      <c r="AD16" s="13" t="n">
+        <v>1.21</v>
+      </c>
       <c r="AE16" s="13" t="n">
-        <v>644</v>
+        <v>-0.04</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>7.76</v>
+        <v>-0.04</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>4266</v>
-      </c>
-      <c r="AH16" s="13" t="inlineStr"/>
+        <v>-0.04</v>
+      </c>
+      <c r="AH16" s="13" t="n">
+        <v>0.71</v>
+      </c>
       <c r="AI16" s="13" t="n">
-        <v>531</v>
+        <v>-0.05</v>
       </c>
       <c r="AJ16" s="13" t="n">
-        <v>6.67</v>
+        <v>-0.05</v>
       </c>
       <c r="AK16" s="13" t="n">
-        <v>18430</v>
-      </c>
-      <c r="AL16" s="13" t="inlineStr"/>
+        <v>-0.05</v>
+      </c>
+      <c r="AL16" s="13" t="n">
+        <v>1.21</v>
+      </c>
       <c r="AM16" s="13" t="n">
-        <v>2544</v>
+        <v>-0.2</v>
       </c>
       <c r="AN16" s="13" t="n">
-        <v>30.64</v>
-      </c>
-      <c r="AO16" s="13" t="inlineStr"/>
+        <v>-0.31</v>
+      </c>
+      <c r="AO16" s="13" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="AP16" s="13" t="n">
-        <v>13.8</v>
+        <v>-16.53</v>
       </c>
       <c r="AQ16" s="13" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AR16" s="13" t="inlineStr"/>
-      <c r="AS16" s="35" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="AT16" s="35" t="n">
-        <v>12.1</v>
-      </c>
+        <v>-25.62</v>
+      </c>
+      <c r="AR16" s="35" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AS16" s="13" t="inlineStr"/>
+      <c r="AT16" s="13" t="inlineStr"/>
       <c r="AU16" s="13" t="inlineStr"/>
       <c r="AV16" s="35" t="n">
-        <v>0.45</v>
+        <v>27.13</v>
       </c>
       <c r="AW16" s="35" t="n">
-        <v>16300</v>
-      </c>
-      <c r="AX16" s="13" t="inlineStr"/>
+        <v>15.23</v>
+      </c>
+      <c r="AX16" s="13" t="n">
+        <v>0.71</v>
+      </c>
       <c r="AY16" s="13" t="n">
-        <v>2176</v>
+        <v>-0.31</v>
       </c>
       <c r="AZ16" s="13" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="BA16" s="13" t="inlineStr"/>
+        <v>-0.29</v>
+      </c>
+      <c r="BA16" s="13" t="n">
+        <v>-0.29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ICICI Pru Life</t>
+          <t>HDB FINANC SER</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -13205,17 +13836,17 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Life Insurance</t>
+          <t>Non Banking Financial Company (NBFC)</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>81526</v>
+        <v>57662</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>562</v>
+        <v>694</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>50.7</v>
+        <v>22.7</v>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
@@ -13224,138 +13855,116 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>3185</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>-754</v>
-      </c>
+        <v>4745</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="n">
-        <v>624</v>
+        <v>751</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>-23.67</v>
-      </c>
+        <v>9.039999999999999</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="n">
-        <v>19.59</v>
+        <v>15.83</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-86.09999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="12" t="n">
-        <v>61.2</v>
+        <v>16.6</v>
       </c>
       <c r="T17" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>-26.92</v>
-      </c>
+        <v>16.5</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="W17" s="4" t="n">
-        <v>-79.7</v>
+        <v>2.05</v>
+      </c>
+      <c r="W17" s="12" t="n">
+        <v>11.2</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="12" t="n">
-        <v>62.1</v>
+        <v>41.4</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA17" s="4" t="n">
-        <v>-26.32</v>
-      </c>
+        <v>35.5</v>
+      </c>
+      <c r="AA17" s="3" t="inlineStr"/>
       <c r="AB17" s="12" t="n">
-        <v>17.14</v>
+        <v>3.38</v>
       </c>
       <c r="AC17" s="12" t="n">
-        <v>22834</v>
-      </c>
-      <c r="AD17" s="3" t="n">
-        <v>741</v>
-      </c>
+        <v>4674</v>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
       <c r="AE17" s="3" t="n">
-        <v>387</v>
+        <v>644</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>2.67</v>
+        <v>7.76</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>15687</v>
-      </c>
-      <c r="AH17" s="3" t="n">
-        <v>415</v>
-      </c>
+        <v>4266</v>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
       <c r="AI17" s="3" t="n">
-        <v>385</v>
+        <v>531</v>
       </c>
       <c r="AJ17" s="3" t="n">
-        <v>2.67</v>
+        <v>6.67</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>63357</v>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>181</v>
-      </c>
+        <v>18430</v>
+      </c>
+      <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="n">
-        <v>1608</v>
+        <v>2544</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="AO17" s="3" t="n">
-        <v>0.29</v>
-      </c>
+        <v>30.64</v>
+      </c>
+      <c r="AO17" s="3" t="inlineStr"/>
       <c r="AP17" s="3" t="n">
-        <v>2.54</v>
+        <v>13.8</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AR17" s="4" t="n">
-        <v>-84.40000000000001</v>
-      </c>
+        <v>13.1</v>
+      </c>
+      <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="12" t="n">
-        <v>35.6</v>
+        <v>16.9</v>
       </c>
       <c r="AT17" s="12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="AU17" s="4" t="n">
-        <v>-1.34</v>
-      </c>
+        <v>12.1</v>
+      </c>
+      <c r="AU17" s="3" t="inlineStr"/>
       <c r="AV17" s="12" t="n">
-        <v>0.86</v>
+        <v>0.45</v>
       </c>
       <c r="AW17" s="12" t="n">
-        <v>70778</v>
-      </c>
-      <c r="AX17" s="3" t="n">
-        <v>1157</v>
-      </c>
+        <v>16300</v>
+      </c>
+      <c r="AX17" s="3" t="inlineStr"/>
       <c r="AY17" s="3" t="n">
-        <v>1186</v>
+        <v>2176</v>
       </c>
       <c r="AZ17" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>27.34</v>
       </c>
       <c r="BA17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Jindal Leasefin</t>
+          <t>ICICI Pru Life</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -13370,139 +13979,157 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Investment Company</t>
+          <t>Life Insurance</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>21</v>
+        <v>81526</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>69.8</v>
+        <v>562</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>539947</v>
-      </c>
+        <v>50.7</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr"/>
       <c r="J18" s="13" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>2.48</v>
+        <v>3185</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>2.38</v>
+        <v>-754</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>1.18</v>
+        <v>624</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>95.97</v>
+        <v>-23.67</v>
       </c>
       <c r="P18" s="13" t="n">
-        <v>47.58</v>
-      </c>
-      <c r="Q18" s="13" t="inlineStr"/>
+        <v>19.59</v>
+      </c>
+      <c r="Q18" s="13" t="n">
+        <v>-86.09999999999999</v>
+      </c>
       <c r="R18" s="13" t="inlineStr"/>
-      <c r="S18" s="13" t="inlineStr"/>
-      <c r="T18" s="13" t="inlineStr"/>
+      <c r="S18" s="35" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="T18" s="35" t="n">
+        <v>61</v>
+      </c>
       <c r="U18" s="14" t="n">
-        <v>-27.84</v>
-      </c>
-      <c r="V18" s="14" t="n">
-        <v>-47.66</v>
-      </c>
-      <c r="W18" s="13" t="inlineStr"/>
+        <v>-26.92</v>
+      </c>
+      <c r="V18" s="35" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="W18" s="14" t="n">
+        <v>-79.7</v>
+      </c>
       <c r="X18" s="13" t="inlineStr"/>
-      <c r="Y18" s="13" t="inlineStr"/>
-      <c r="Z18" s="13" t="inlineStr"/>
+      <c r="Y18" s="35" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="Z18" s="35" t="n">
+        <v>61</v>
+      </c>
       <c r="AA18" s="14" t="n">
-        <v>-7.62</v>
-      </c>
-      <c r="AB18" s="14" t="n">
-        <v>-26.67</v>
-      </c>
-      <c r="AC18" s="14" t="n">
-        <v>-0.21</v>
+        <v>-26.32</v>
+      </c>
+      <c r="AB18" s="35" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AC18" s="35" t="n">
+        <v>22834</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>-0.26</v>
+        <v>741</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>-0.2</v>
+        <v>387</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>-0.66</v>
+        <v>2.67</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>-1.67</v>
+        <v>15687</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>-1.73</v>
+        <v>415</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>-1.24</v>
+        <v>385</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>-4.12</v>
+        <v>2.67</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>2.39</v>
+        <v>63357</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>2.13</v>
+        <v>181</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>0.92</v>
+        <v>1608</v>
       </c>
       <c r="AN18" s="13" t="n">
-        <v>3.06</v>
+        <v>11.09</v>
       </c>
       <c r="AO18" s="13" t="n">
-        <v>89.12</v>
+        <v>0.29</v>
       </c>
       <c r="AP18" s="13" t="n">
-        <v>38.49</v>
-      </c>
-      <c r="AQ18" s="13" t="inlineStr"/>
-      <c r="AR18" s="13" t="inlineStr"/>
-      <c r="AS18" s="13" t="inlineStr"/>
-      <c r="AT18" s="13" t="inlineStr"/>
+        <v>2.54</v>
+      </c>
+      <c r="AQ18" s="13" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AR18" s="14" t="n">
+        <v>-84.40000000000001</v>
+      </c>
+      <c r="AS18" s="35" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="AT18" s="35" t="n">
+        <v>35.2</v>
+      </c>
       <c r="AU18" s="14" t="n">
-        <v>-16.68</v>
-      </c>
-      <c r="AV18" s="14" t="n">
-        <v>-42.74</v>
-      </c>
-      <c r="AW18" s="14" t="n">
-        <v>-2.93</v>
+        <v>-1.34</v>
+      </c>
+      <c r="AV18" s="35" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW18" s="35" t="n">
+        <v>70778</v>
       </c>
       <c r="AX18" s="13" t="n">
-        <v>-3.1</v>
+        <v>1157</v>
       </c>
       <c r="AY18" s="13" t="n">
-        <v>-2.38</v>
+        <v>1186</v>
       </c>
       <c r="AZ18" s="13" t="n">
-        <v>-7.91</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Ind Bank Housing</t>
+          <t>Jindal Leasefin</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -13517,18 +14144,20 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Housing Finance Company</t>
+          <t>Investment Company</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45.5</v>
+        <v>21</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
+        <v>69.8</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="I19" s="3" t="n">
-        <v>523465</v>
+        <v>539947</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -13536,100 +14165,118 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.23</v>
+        <v>2.38</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.02</v>
+        <v>1.18</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
+        <v>3.92</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>47.58</v>
+      </c>
       <c r="Q19" s="3" t="inlineStr"/>
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr"/>
       <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="U19" s="4" t="n">
+        <v>-27.84</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>-47.66</v>
+      </c>
       <c r="W19" s="3" t="inlineStr"/>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="inlineStr"/>
       <c r="Z19" s="3" t="inlineStr"/>
-      <c r="AA19" s="3" t="inlineStr"/>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="12" t="n">
-        <v>0</v>
+      <c r="AA19" s="4" t="n">
+        <v>-7.62</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>-26.67</v>
+      </c>
+      <c r="AC19" s="4" t="n">
+        <v>-0.21</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.66</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AH19" s="3" t="n">
-        <v>-0.14</v>
+        <v>-1.73</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>-0.05</v>
+        <v>-1.24</v>
       </c>
       <c r="AJ19" s="3" t="n">
-        <v>-0.05</v>
+        <v>-4.12</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>-0.6</v>
+        <v>2.13</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.92</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="n">
-        <v>-100</v>
-      </c>
+        <v>3.06</v>
+      </c>
+      <c r="AO19" s="3" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="AP19" s="3" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr"/>
       <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
-      <c r="AV19" s="3" t="inlineStr"/>
-      <c r="AW19" s="12" t="n">
-        <v>0.28</v>
+      <c r="AU19" s="4" t="n">
+        <v>-16.68</v>
+      </c>
+      <c r="AV19" s="4" t="n">
+        <v>-42.74</v>
+      </c>
+      <c r="AW19" s="4" t="n">
+        <v>-2.93</v>
       </c>
       <c r="AX19" s="3" t="n">
-        <v>-0.31</v>
+        <v>-3.1</v>
       </c>
       <c r="AY19" s="3" t="n">
-        <v>-0.31</v>
+        <v>-2.38</v>
       </c>
       <c r="AZ19" s="3" t="n">
-        <v>-0.31</v>
+        <v>-7.91</v>
       </c>
       <c r="BA19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Kapil Raj Financ</t>
+          <t>Ind Bank Housing</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -13644,20 +14291,18 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Non Banking Financial Company (NBFC)</t>
+          <t>Housing Finance Company</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>34</v>
+        <v>45.5</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>61.9</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="H20" s="13" t="inlineStr"/>
       <c r="I20" s="13" t="n">
-        <v>539679</v>
+        <v>523465</v>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
@@ -13667,18 +14312,18 @@
       <c r="K20" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="13" t="inlineStr"/>
+      <c r="L20" s="13" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="M20" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O20" s="13" t="inlineStr"/>
       <c r="P20" s="13" t="inlineStr"/>
-      <c r="Q20" s="13" t="n">
-        <v>-100</v>
-      </c>
+      <c r="Q20" s="13" t="inlineStr"/>
       <c r="R20" s="13" t="inlineStr"/>
       <c r="S20" s="13" t="inlineStr"/>
       <c r="T20" s="13" t="inlineStr"/>
@@ -13691,70 +14336,74 @@
       <c r="AA20" s="13" t="inlineStr"/>
       <c r="AB20" s="13" t="inlineStr"/>
       <c r="AC20" s="35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AD20" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="13" t="n">
+        <v>-0.11</v>
+      </c>
       <c r="AE20" s="13" t="n">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="AF20" s="13" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AG20" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" s="13" t="inlineStr"/>
+      <c r="AH20" s="13" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="AI20" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="AJ20" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AK20" s="13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AL20" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="13" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AM20" s="13" t="n">
-        <v>0.55</v>
+        <v>-0.09</v>
       </c>
       <c r="AN20" s="13" t="n">
-        <v>0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="AO20" s="13" t="inlineStr"/>
-      <c r="AP20" s="13" t="n">
-        <v>68.75</v>
-      </c>
+      <c r="AP20" s="13" t="inlineStr"/>
       <c r="AQ20" s="13" t="n">
-        <v>321.1</v>
+        <v>-100</v>
       </c>
       <c r="AR20" s="13" t="inlineStr"/>
       <c r="AS20" s="13" t="inlineStr"/>
       <c r="AT20" s="13" t="inlineStr"/>
       <c r="AU20" s="13" t="inlineStr"/>
-      <c r="AV20" s="35" t="n">
-        <v>74.01000000000001</v>
-      </c>
+      <c r="AV20" s="13" t="inlineStr"/>
       <c r="AW20" s="35" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AX20" s="13" t="inlineStr"/>
+        <v>0.28</v>
+      </c>
+      <c r="AX20" s="13" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="AY20" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.31</v>
       </c>
       <c r="AZ20" s="13" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="BA20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Nikki Glob.Fin.</t>
+          <t>Kapil Raj Financ</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -13773,16 +14422,16 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>7.54</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>22</v>
+        <v>3.11</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>35.9</v>
+        <v>61.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>531272</v>
+        <v>539679</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -13790,20 +14439,20 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.91</v>
+        <v>-0.01</v>
       </c>
       <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="n">
+        <v>-100</v>
+      </c>
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr"/>
       <c r="T21" s="3" t="inlineStr"/>
@@ -13816,70 +14465,70 @@
       <c r="AA21" s="3" t="inlineStr"/>
       <c r="AB21" s="3" t="inlineStr"/>
       <c r="AC21" s="12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD21" s="3" t="inlineStr"/>
       <c r="AE21" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.28</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="AG21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH21" s="3" t="inlineStr"/>
       <c r="AI21" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ21" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="n">
-        <v>0.21</v>
+        <v>0.55</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>0.61</v>
+        <v>0.05</v>
       </c>
       <c r="AO21" s="3" t="inlineStr"/>
       <c r="AP21" s="3" t="n">
-        <v>52.5</v>
+        <v>68.75</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>185.7</v>
+        <v>321.1</v>
       </c>
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr"/>
       <c r="AT21" s="3" t="inlineStr"/>
       <c r="AU21" s="3" t="inlineStr"/>
       <c r="AV21" s="12" t="n">
-        <v>73.93000000000001</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AW21" s="12" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="AX21" s="3" t="inlineStr"/>
       <c r="AY21" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AZ21" s="3" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="BA21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Jindal Leasefin</t>
+          <t>Nikki Glob.Fin.</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -13894,141 +14543,117 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Investment Company</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr"/>
+          <t>Non Banking Financial Company (NBFC)</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>7.54</v>
+      </c>
       <c r="G22" s="13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>69.8</v>
+        <v>35.9</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>22.8</v>
+        <v>531272</v>
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>539947</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="L22" s="13" t="n">
-        <v>2.48</v>
-      </c>
+      <c r="K22" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L22" s="13" t="inlineStr"/>
       <c r="M22" s="13" t="n">
-        <v>2.38</v>
+        <v>0.31</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="O22" s="13" t="n">
-        <v>3.92</v>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="O22" s="13" t="inlineStr"/>
       <c r="P22" s="13" t="n">
-        <v>95.97</v>
-      </c>
-      <c r="Q22" s="13" t="n">
-        <v>47.58</v>
-      </c>
+        <v>77.5</v>
+      </c>
+      <c r="Q22" s="13" t="inlineStr"/>
       <c r="R22" s="13" t="inlineStr"/>
       <c r="S22" s="13" t="inlineStr"/>
       <c r="T22" s="13" t="inlineStr"/>
       <c r="U22" s="13" t="inlineStr"/>
-      <c r="V22" s="14" t="n">
-        <v>-27.84</v>
-      </c>
-      <c r="W22" s="14" t="n">
-        <v>-47.66</v>
-      </c>
+      <c r="V22" s="13" t="inlineStr"/>
+      <c r="W22" s="13" t="inlineStr"/>
       <c r="X22" s="13" t="inlineStr"/>
       <c r="Y22" s="13" t="inlineStr"/>
       <c r="Z22" s="13" t="inlineStr"/>
       <c r="AA22" s="13" t="inlineStr"/>
-      <c r="AB22" s="14" t="n">
-        <v>-7.62</v>
-      </c>
-      <c r="AC22" s="14" t="n">
-        <v>-26.67</v>
-      </c>
-      <c r="AD22" s="13" t="n">
-        <v>-0.21</v>
-      </c>
+      <c r="AB22" s="13" t="inlineStr"/>
+      <c r="AC22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="13" t="inlineStr"/>
       <c r="AE22" s="13" t="n">
-        <v>-0.26</v>
+        <v>-0.02</v>
       </c>
       <c r="AF22" s="13" t="n">
-        <v>-0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="AG22" s="13" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="AH22" s="13" t="n">
-        <v>-1.67</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="13" t="inlineStr"/>
       <c r="AI22" s="13" t="n">
-        <v>-1.73</v>
+        <v>-0.05</v>
       </c>
       <c r="AJ22" s="13" t="n">
-        <v>-1.24</v>
+        <v>-0.15</v>
       </c>
       <c r="AK22" s="13" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="AL22" s="13" t="n">
-        <v>2.39</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="AL22" s="13" t="inlineStr"/>
       <c r="AM22" s="13" t="n">
-        <v>2.13</v>
+        <v>0.21</v>
       </c>
       <c r="AN22" s="13" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AO22" s="13" t="n">
-        <v>3.06</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="AO22" s="13" t="inlineStr"/>
       <c r="AP22" s="13" t="n">
-        <v>89.12</v>
+        <v>52.5</v>
       </c>
       <c r="AQ22" s="13" t="n">
-        <v>38.49</v>
+        <v>185.7</v>
       </c>
       <c r="AR22" s="13" t="inlineStr"/>
       <c r="AS22" s="13" t="inlineStr"/>
       <c r="AT22" s="13" t="inlineStr"/>
       <c r="AU22" s="13" t="inlineStr"/>
-      <c r="AV22" s="14" t="n">
-        <v>-16.68</v>
-      </c>
-      <c r="AW22" s="14" t="n">
-        <v>-42.74</v>
-      </c>
-      <c r="AX22" s="13" t="n">
-        <v>-2.93</v>
-      </c>
+      <c r="AV22" s="35" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="AW22" s="35" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX22" s="13" t="inlineStr"/>
       <c r="AY22" s="13" t="n">
-        <v>-3.1</v>
+        <v>-0.03</v>
       </c>
       <c r="AZ22" s="13" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="BA22" s="13" t="n">
-        <v>-7.91</v>
-      </c>
+        <v>-0.09</v>
+      </c>
+      <c r="BA22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>13 Apr 2026</t>
+          <t>08 Apr 2026</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Ind Bank Housing</t>
+          <t>Jindal Leasefin</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -14043,20 +14668,22 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Housing Finance Company</t>
+          <t>Investment Company</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>45.4</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
+        <v>69.8</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>523465</t>
+          <t>539947</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -14065,99 +14692,117 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-0.23</v>
+        <v>2.38</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>-0.02</v>
+        <v>1.18</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
+        <v>3.92</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>47.58</v>
+      </c>
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="inlineStr"/>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
+      <c r="V23" s="4" t="n">
+        <v>-27.84</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <v>-47.66</v>
+      </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="inlineStr"/>
       <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr"/>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AB23" s="4" t="n">
+        <v>-7.62</v>
+      </c>
+      <c r="AC23" s="4" t="n">
+        <v>-26.67</v>
+      </c>
       <c r="AD23" s="3" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>0.06</v>
+        <v>-0.66</v>
       </c>
       <c r="AH23" s="3" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>-0.14</v>
+        <v>-1.73</v>
       </c>
       <c r="AJ23" s="3" t="n">
-        <v>-0.05</v>
+        <v>-1.24</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>-0.05</v>
+        <v>-4.12</v>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM23" s="3" t="n">
-        <v>-0.6</v>
+        <v>2.13</v>
       </c>
       <c r="AN23" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.92</v>
       </c>
       <c r="AO23" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
-      <c r="AR23" s="4" t="n">
-        <v>-100</v>
-      </c>
+        <v>3.06</v>
+      </c>
+      <c r="AP23" s="3" t="n">
+        <v>89.12</v>
+      </c>
+      <c r="AQ23" s="3" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="AR23" s="3" t="inlineStr"/>
       <c r="AS23" s="3" t="inlineStr"/>
       <c r="AT23" s="3" t="inlineStr"/>
       <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr"/>
-      <c r="AW23" s="3" t="inlineStr"/>
+      <c r="AV23" s="4" t="n">
+        <v>-16.68</v>
+      </c>
+      <c r="AW23" s="4" t="n">
+        <v>-42.74</v>
+      </c>
       <c r="AX23" s="3" t="n">
-        <v>0.28</v>
+        <v>-2.93</v>
       </c>
       <c r="AY23" s="3" t="n">
-        <v>-0.31</v>
+        <v>-3.1</v>
       </c>
       <c r="AZ23" s="3" t="n">
-        <v>-0.31</v>
+        <v>-2.38</v>
       </c>
       <c r="BA23" s="3" t="n">
-        <v>-0.31</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>14 Apr 2026</t>
+          <t>13 Apr 2026</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>Kapil Raj Financ</t>
+          <t>Ind Bank Housing</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -14172,22 +14817,20 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Non Banking Financial Company (NBFC)</t>
+          <t>Housing Finance Company</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr"/>
       <c r="G24" s="13" t="n">
-        <v>34.1</v>
+        <v>45.4</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>62.1</v>
-      </c>
+        <v>45.4</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr"/>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>539679</t>
+          <t>523465</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
@@ -14198,18 +14841,18 @@
       <c r="L24" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="13" t="inlineStr"/>
+      <c r="M24" s="13" t="n">
+        <v>-0.23</v>
+      </c>
       <c r="N24" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="P24" s="13" t="inlineStr"/>
       <c r="Q24" s="13" t="inlineStr"/>
-      <c r="R24" s="14" t="n">
-        <v>-100</v>
-      </c>
+      <c r="R24" s="13" t="inlineStr"/>
       <c r="S24" s="13" t="inlineStr"/>
       <c r="T24" s="13" t="inlineStr"/>
       <c r="U24" s="13" t="inlineStr"/>
@@ -14222,69 +14865,73 @@
       <c r="AB24" s="13" t="inlineStr"/>
       <c r="AC24" s="13" t="inlineStr"/>
       <c r="AD24" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AE24" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="13" t="n">
+        <v>-0.11</v>
+      </c>
       <c r="AF24" s="13" t="n">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="AG24" s="13" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AH24" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="AI24" s="13" t="inlineStr"/>
+      <c r="AI24" s="13" t="n">
+        <v>-0.14</v>
+      </c>
       <c r="AJ24" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="AK24" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AL24" s="13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AM24" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="13" t="n">
+        <v>-0.6</v>
+      </c>
       <c r="AN24" s="13" t="n">
-        <v>0.55</v>
+        <v>-0.09</v>
       </c>
       <c r="AO24" s="13" t="n">
-        <v>0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="AP24" s="13" t="inlineStr"/>
-      <c r="AQ24" s="13" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="AR24" s="35" t="n">
-        <v>321.1</v>
+      <c r="AQ24" s="13" t="inlineStr"/>
+      <c r="AR24" s="14" t="n">
+        <v>-100</v>
       </c>
       <c r="AS24" s="13" t="inlineStr"/>
       <c r="AT24" s="13" t="inlineStr"/>
       <c r="AU24" s="13" t="inlineStr"/>
       <c r="AV24" s="13" t="inlineStr"/>
-      <c r="AW24" s="35" t="n">
-        <v>74.01000000000001</v>
-      </c>
+      <c r="AW24" s="13" t="inlineStr"/>
       <c r="AX24" s="13" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AY24" s="13" t="inlineStr"/>
+        <v>0.28</v>
+      </c>
+      <c r="AY24" s="13" t="n">
+        <v>-0.31</v>
+      </c>
       <c r="AZ24" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.31</v>
       </c>
       <c r="BA24" s="13" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>14 Apr 2026</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Nikki Glob.Fin.</t>
+          <t>Kapil Raj Financ</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -14304,17 +14951,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="n">
-        <v>7.54</v>
+        <v>34.1</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>22</v>
+        <v>3.12</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>35.9</v>
+        <v>62.1</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>531272</t>
+          <t>539679</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -14323,20 +14970,20 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M25" s="3" t="inlineStr"/>
       <c r="N25" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0.91</v>
+        <v>-0.01</v>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="R25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="4" t="n">
+        <v>-100</v>
+      </c>
       <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr"/>
       <c r="U25" s="3" t="inlineStr"/>
@@ -14349,62 +14996,189 @@
       <c r="AB25" s="3" t="inlineStr"/>
       <c r="AC25" s="3" t="inlineStr"/>
       <c r="AD25" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AE25" s="3" t="inlineStr"/>
       <c r="AF25" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.28</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="AH25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="inlineStr"/>
       <c r="AJ25" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.01</v>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AM25" s="3" t="inlineStr"/>
       <c r="AN25" s="3" t="n">
-        <v>0.21</v>
+        <v>0.55</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>0.61</v>
+        <v>0.05</v>
       </c>
       <c r="AP25" s="3" t="inlineStr"/>
       <c r="AQ25" s="3" t="n">
-        <v>52.5</v>
+        <v>68.75</v>
       </c>
       <c r="AR25" s="12" t="n">
-        <v>185.7</v>
+        <v>321.1</v>
       </c>
       <c r="AS25" s="3" t="inlineStr"/>
       <c r="AT25" s="3" t="inlineStr"/>
       <c r="AU25" s="3" t="inlineStr"/>
       <c r="AV25" s="3" t="inlineStr"/>
       <c r="AW25" s="12" t="n">
-        <v>73.93000000000001</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="AX25" s="3" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="AY25" s="3" t="inlineStr"/>
       <c r="AZ25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BA25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>15 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Nikki Glob.Fin.</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Non Banking Financial Company (NBFC)</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr"/>
+      <c r="G26" s="13" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>531272</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M26" s="13" t="inlineStr"/>
+      <c r="N26" s="13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P26" s="13" t="inlineStr"/>
+      <c r="Q26" s="13" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="R26" s="13" t="inlineStr"/>
+      <c r="S26" s="13" t="inlineStr"/>
+      <c r="T26" s="13" t="inlineStr"/>
+      <c r="U26" s="13" t="inlineStr"/>
+      <c r="V26" s="13" t="inlineStr"/>
+      <c r="W26" s="13" t="inlineStr"/>
+      <c r="X26" s="13" t="inlineStr"/>
+      <c r="Y26" s="13" t="inlineStr"/>
+      <c r="Z26" s="13" t="inlineStr"/>
+      <c r="AA26" s="13" t="inlineStr"/>
+      <c r="AB26" s="13" t="inlineStr"/>
+      <c r="AC26" s="13" t="inlineStr"/>
+      <c r="AD26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="13" t="inlineStr"/>
+      <c r="AF26" s="13" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AG26" s="13" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AH26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="13" t="inlineStr"/>
+      <c r="AJ26" s="13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK26" s="13" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AL26" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM26" s="13" t="inlineStr"/>
+      <c r="AN26" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AO26" s="13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AP26" s="13" t="inlineStr"/>
+      <c r="AQ26" s="13" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AR26" s="35" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="AS26" s="13" t="inlineStr"/>
+      <c r="AT26" s="13" t="inlineStr"/>
+      <c r="AU26" s="13" t="inlineStr"/>
+      <c r="AV26" s="13" t="inlineStr"/>
+      <c r="AW26" s="35" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="AX26" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AY26" s="13" t="inlineStr"/>
+      <c r="AZ26" s="13" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BA25" s="3" t="n">
+      <c r="BA26" s="13" t="n">
         <v>-0.09</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BA25"/>
+  <autoFilter ref="A2:BA26"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AZ1"/>
     <mergeCell ref="A1:BA1"/>
@@ -15022,7 +15796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA9"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15851,12 +16625,12 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>09 Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>G M Breweries</t>
+          <t>Bajaj Consumer</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -15871,22 +16645,22 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Breweries &amp; Distilleries</t>
+          <t>Personal Care</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="n">
-        <v>2231</v>
+        <v>6175</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>977</v>
+        <v>472</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>14.2</v>
+        <v>32.5</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>GMBREW</t>
+          <t>BAJAJCON</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -15895,141 +16669,141 @@
         </is>
       </c>
       <c r="L6" s="13" t="n">
-        <v>202</v>
+        <v>327</v>
       </c>
       <c r="M6" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="O6" s="13" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="Q6" s="13" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="R6" s="35" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S6" s="35" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T6" s="35" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U6" s="35" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V6" s="35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W6" s="35" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="X6" s="35" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Y6" s="35" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Z6" s="35" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AA6" s="35" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AB6" s="35" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AC6" s="35" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AD6" s="13" t="n">
+        <v>306</v>
+      </c>
+      <c r="AE6" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF6" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG6" s="13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH6" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="AI6" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ6" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK6" s="13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL6" s="13" t="n">
+        <v>1165</v>
+      </c>
+      <c r="AM6" s="13" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN6" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO6" s="13" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AP6" s="13" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AQ6" s="13" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AR6" s="35" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AS6" s="35" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AT6" s="35" t="n">
         <v>52</v>
       </c>
-      <c r="N6" s="13" t="n">
-        <v>54</v>
-      </c>
-      <c r="O6" s="13" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="P6" s="13" t="n">
-        <v>25.74</v>
-      </c>
-      <c r="Q6" s="13" t="n">
-        <v>26.73</v>
-      </c>
-      <c r="R6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="14" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="T6" s="35" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="U6" s="35" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="V6" s="14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W6" s="35" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="X6" s="35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y6" s="35" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="Z6" s="14" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AA6" s="14" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AB6" s="35" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="AC6" s="14" t="n">
-        <v>-8.77</v>
-      </c>
-      <c r="AD6" s="13" t="n">
-        <v>202</v>
-      </c>
-      <c r="AE6" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="AF6" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG6" s="13" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="AH6" s="13" t="n">
-        <v>169</v>
-      </c>
-      <c r="AI6" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ6" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK6" s="13" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="AL6" s="13" t="n">
-        <v>748</v>
-      </c>
-      <c r="AM6" s="13" t="n">
-        <v>181</v>
-      </c>
-      <c r="AN6" s="13" t="n">
-        <v>157</v>
-      </c>
-      <c r="AO6" s="13" t="n">
-        <v>68.64</v>
-      </c>
-      <c r="AP6" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AQ6" s="13" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="AR6" s="35" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="AS6" s="35" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="AT6" s="35" t="n">
-        <v>21.7</v>
-      </c>
       <c r="AU6" s="35" t="n">
-        <v>21.5</v>
+        <v>59.3</v>
       </c>
       <c r="AV6" s="35" t="n">
-        <v>5.68</v>
+        <v>5.71</v>
       </c>
       <c r="AW6" s="35" t="n">
-        <v>0.74</v>
+        <v>3.36</v>
       </c>
       <c r="AX6" s="13" t="n">
-        <v>637</v>
+        <v>965</v>
       </c>
       <c r="AY6" s="13" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AZ6" s="13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="BA6" s="13" t="n">
-        <v>56.48</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>09 Apr 2026</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Lotus Chocolate</t>
+          <t>G M Breweries</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -16044,22 +16818,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Breweries &amp; Distilleries</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="n">
-        <v>966</v>
+        <v>2231</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>752</v>
+        <v>977</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>9655</v>
+        <v>14.2</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>523475</t>
+          <t>GMBREW</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -16068,127 +16842,141 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>126.78</v>
+        <v>202</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>-12.25</v>
+        <v>52</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-4.47</v>
+        <v>54</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-3.48</v>
+        <v>23.67</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-9.66</v>
+        <v>25.74</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr"/>
+        <v>26.73</v>
+      </c>
+      <c r="R7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="T7" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="U7" s="12" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V7" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
-        <v>-13.25</v>
+        <v>-0.5</v>
+      </c>
+      <c r="W7" s="12" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="X7" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AB7" s="12" t="n">
+        <v>8.58</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>-4.43</v>
+        <v>-8.77</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>133.63</v>
+        <v>202</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>-10.9</v>
+        <v>53</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.14</v>
+        <v>42</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.11</v>
+        <v>18.39</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>157.45</v>
+        <v>169</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>5.66</v>
+        <v>29</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>1.42</v>
+        <v>60</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>1.11</v>
+        <v>26.46</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>580</v>
+        <v>748</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>-15</v>
+        <v>181</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>0.08</v>
+        <v>68.64</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>-2.59</v>
+        <v>24.2</v>
       </c>
       <c r="AQ7" s="3" t="n">
-        <v>0</v>
+        <v>20.99</v>
       </c>
       <c r="AR7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="AU7" s="4" t="n">
-        <v>-99.40000000000001</v>
-      </c>
-      <c r="AV7" s="4" t="n">
-        <v>-7.99</v>
-      </c>
-      <c r="AW7" s="4" t="n">
-        <v>-2.96</v>
+        <v>17.4</v>
+      </c>
+      <c r="AS7" s="12" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AT7" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AU7" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AV7" s="12" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AW7" s="12" t="n">
+        <v>0.74</v>
       </c>
       <c r="AX7" s="3" t="n">
-        <v>574</v>
+        <v>637</v>
       </c>
       <c r="AY7" s="3" t="n">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="AZ7" s="3" t="n">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="BA7" s="3" t="n">
-        <v>13.42</v>
+        <v>56.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>10 Apr 2026</t>
+          <t>15 Apr 2026</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Agri-Tech India</t>
+          <t>Lotus Chocolate</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -16203,141 +16991,151 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Other Agricultural Products</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>72.59999999999999</v>
-      </c>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="13" t="n">
-        <v>122</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
+        <v>966</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>752</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>9655</v>
+      </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
+          <t>523475</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="K8" s="13" t="n">
-        <v>0.08</v>
-      </c>
       <c r="L8" s="13" t="n">
-        <v>-0.23</v>
+        <v>126.78</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>-0.27</v>
+        <v>-12.25</v>
       </c>
       <c r="N8" s="13" t="n">
-        <v>-0.45</v>
+        <v>-4.47</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>-287.5</v>
+        <v>-3.48</v>
       </c>
       <c r="P8" s="13" t="n">
-        <v>-337.5</v>
+        <v>-9.66</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="R8" s="13" t="inlineStr"/>
+        <v>-3.53</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <v>-5.1</v>
+      </c>
       <c r="S8" s="13" t="inlineStr"/>
       <c r="T8" s="13" t="inlineStr"/>
-      <c r="U8" s="35" t="n">
-        <v>872.5</v>
-      </c>
-      <c r="V8" s="35" t="n">
-        <v>842.5</v>
-      </c>
-      <c r="W8" s="35" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="X8" s="13" t="inlineStr"/>
+      <c r="U8" s="13" t="inlineStr"/>
+      <c r="V8" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="W8" s="14" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="X8" s="14" t="n">
+        <v>-19.5</v>
+      </c>
       <c r="Y8" s="13" t="inlineStr"/>
       <c r="Z8" s="13" t="inlineStr"/>
-      <c r="AA8" s="35" t="n">
-        <v>45.83</v>
-      </c>
-      <c r="AB8" s="35" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="AC8" s="35" t="n">
-        <v>0.05</v>
+      <c r="AA8" s="13" t="inlineStr"/>
+      <c r="AB8" s="14" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="AC8" s="14" t="n">
+        <v>-4.43</v>
       </c>
       <c r="AD8" s="13" t="n">
-        <v>-0.58</v>
+        <v>133.63</v>
       </c>
       <c r="AE8" s="13" t="n">
-        <v>-0.59</v>
+        <v>-10.9</v>
       </c>
       <c r="AF8" s="13" t="n">
-        <v>-0.99</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" s="13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AH8" s="13" t="n">
-        <v>-0.2</v>
+        <v>157.45</v>
       </c>
       <c r="AI8" s="13" t="n">
-        <v>-0.26</v>
+        <v>5.66</v>
       </c>
       <c r="AJ8" s="13" t="n">
-        <v>-0.44</v>
+        <v>1.42</v>
       </c>
       <c r="AK8" s="13" t="n">
-        <v>0.28</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" s="13" t="n">
-        <v>-1.05</v>
+        <v>580</v>
       </c>
       <c r="AM8" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-15</v>
       </c>
       <c r="AN8" s="13" t="n">
-        <v>-1.58</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="13" t="n">
-        <v>-375</v>
+        <v>0.08</v>
       </c>
       <c r="AP8" s="13" t="n">
-        <v>-335.71</v>
+        <v>-2.59</v>
       </c>
       <c r="AQ8" s="13" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="AR8" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="AS8" s="13" t="inlineStr"/>
-      <c r="AT8" s="13" t="inlineStr"/>
-      <c r="AU8" s="35" t="n">
-        <v>208.33</v>
-      </c>
-      <c r="AV8" s="35" t="n">
-        <v>280.96</v>
-      </c>
-      <c r="AW8" s="35" t="n">
-        <v>0.18</v>
+      <c r="AT8" s="14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="AU8" s="14" t="n">
+        <v>-99.40000000000001</v>
+      </c>
+      <c r="AV8" s="14" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="AW8" s="14" t="n">
+        <v>-2.96</v>
       </c>
       <c r="AX8" s="13" t="n">
-        <v>-1.05</v>
+        <v>574</v>
       </c>
       <c r="AY8" s="13" t="n">
-        <v>-1.11</v>
+        <v>31</v>
       </c>
       <c r="AZ8" s="13" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="BA8" s="13" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="BA8" s="13" t="n">
+        <v>13.42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>15 Apr 2026</t>
+          <t>10 Apr 2026</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Lotus Chocolate</t>
+          <t>Agri-Tech India</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -16352,142 +17150,291 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Packaged Foods</t>
+          <t>Other Agricultural Products</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>971</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>756</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>9707</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>523475</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>126.78</v>
+        <v>0.08</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-12.25</v>
+        <v>-0.23</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>-4.47</v>
+        <v>-0.27</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-3.48</v>
+        <v>-0.45</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-9.66</v>
+        <v>-287.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>-3.53</v>
+        <v>-337.5</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>-5.1</v>
+        <v>60</v>
       </c>
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>-3.63</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>-19.5</v>
+      <c r="U9" s="12" t="n">
+        <v>872.5</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <v>842.5</v>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>33.3</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="inlineStr"/>
       <c r="Z9" s="3" t="inlineStr"/>
-      <c r="AA9" s="4" t="n">
-        <v>-13.25</v>
-      </c>
-      <c r="AB9" s="4" t="n">
-        <v>-4.43</v>
+      <c r="AA9" s="12" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="AB9" s="12" t="n">
+        <v>95.83</v>
       </c>
       <c r="AC9" s="12" t="n">
-        <v>133.63</v>
+        <v>0.05</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>-10.9</v>
+        <v>-0.58</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.14</v>
+        <v>-0.59</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.11</v>
+        <v>-0.99</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>157.45</v>
+        <v>0.06</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>5.66</v>
+        <v>-0.2</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>1.42</v>
+        <v>-0.26</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>1.11</v>
+        <v>-0.44</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>580</v>
+        <v>0.28</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>-15</v>
+        <v>-1.05</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.08</v>
+        <v>-1.58</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-2.59</v>
+        <v>-375</v>
       </c>
       <c r="AP9" s="3" t="n">
-        <v>0</v>
+        <v>-335.71</v>
       </c>
       <c r="AQ9" s="3" t="n">
-        <v>1</v>
+        <v>55.6</v>
       </c>
       <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="AT9" s="4" t="n">
-        <v>-99.40000000000001</v>
-      </c>
-      <c r="AU9" s="4" t="n">
-        <v>-7.99</v>
-      </c>
-      <c r="AV9" s="4" t="n">
-        <v>-2.96</v>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="12" t="n">
+        <v>208.33</v>
+      </c>
+      <c r="AV9" s="12" t="n">
+        <v>280.96</v>
       </c>
       <c r="AW9" s="12" t="n">
-        <v>574</v>
+        <v>0.18</v>
       </c>
       <c r="AX9" s="3" t="n">
-        <v>31</v>
+        <v>-1.05</v>
       </c>
       <c r="AY9" s="3" t="n">
-        <v>17</v>
+        <v>-1.11</v>
       </c>
       <c r="AZ9" s="3" t="n">
-        <v>13.42</v>
+        <v>-1.87</v>
       </c>
       <c r="BA9" s="3" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>15 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Lotus Chocolate</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>971</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>756</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>9707</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>523475</v>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>-12.25</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>-9.66</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="R10" s="13" t="inlineStr"/>
+      <c r="S10" s="13" t="inlineStr"/>
+      <c r="T10" s="13" t="inlineStr"/>
+      <c r="U10" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V10" s="14" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="W10" s="14" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="X10" s="13" t="inlineStr"/>
+      <c r="Y10" s="13" t="inlineStr"/>
+      <c r="Z10" s="13" t="inlineStr"/>
+      <c r="AA10" s="14" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="AB10" s="14" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="AC10" s="35" t="n">
+        <v>133.63</v>
+      </c>
+      <c r="AD10" s="13" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="AE10" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AF10" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG10" s="13" t="n">
+        <v>157.45</v>
+      </c>
+      <c r="AH10" s="13" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AI10" s="13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ10" s="13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK10" s="13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AL10" s="13" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AM10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AO10" s="13" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="AP10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="13" t="inlineStr"/>
+      <c r="AS10" s="14" t="n">
+        <v>-100</v>
+      </c>
+      <c r="AT10" s="14" t="n">
+        <v>-99.40000000000001</v>
+      </c>
+      <c r="AU10" s="14" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="AV10" s="14" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="AW10" s="35" t="n">
+        <v>574</v>
+      </c>
+      <c r="AX10" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY10" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ10" s="13" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="BA10" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:BA9"/>
+  <autoFilter ref="A2:BA10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AZ1"/>
     <mergeCell ref="A1:BA1"/>
@@ -16502,7 +17449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA4"/>
+  <dimension ref="A1:BA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17159,8 +18106,173 @@
       </c>
       <c r="BA4" s="13" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>M B Agro Prod.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="n">
+        <v>4430</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>506</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="T5" s="12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U5" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="W5" s="12" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="X5" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA5" s="12" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="AB5" s="4" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>612</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>297</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK5" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL5" s="3" t="n">
+        <v>1867</v>
+      </c>
+      <c r="AM5" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AP5" s="3" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AQ5" s="3" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AR5" s="12" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AS5" s="12" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AT5" s="12" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="AU5" s="12" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="AV5" s="4" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AW5" s="12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX5" s="3" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AY5" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ5" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="BA5" s="3" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:BA4"/>
+  <autoFilter ref="A2:BA5"/>
   <mergeCells count="2">
     <mergeCell ref="A1:AZ1"/>
     <mergeCell ref="A1:BA1"/>

--- a/results_logic/Results_By_Sector.xlsx
+++ b/results_logic/Results_By_Sector.xlsx
@@ -3579,10 +3579,10 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>1177</v>
+        <v>1146</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>46.4</v>
+        <v>45.4</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="G4" s="13" t="n">
-        <v>162055</v>
+        <v>164985</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>3279</v>
+        <v>3339</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -4909,13 +4909,13 @@
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>11064</v>
+        <v>11658</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1060</v>
+        <v>1116</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -5251,13 +5251,13 @@
       </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="n">
-        <v>4947</v>
+        <v>4924</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>4072</v>
+        <v>4053</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -5424,13 +5424,13 @@
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="n">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>1645</v>
+        <v>1658</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -5601,13 +5601,13 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>9153</v>
+        <v>9251</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -6362,10 +6362,10 @@
       </c>
       <c r="F12" s="13" t="inlineStr"/>
       <c r="G12" s="13" t="n">
-        <v>28.2</v>
+        <v>28.5</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="I12" s="13" t="inlineStr"/>
       <c r="J12" s="13" t="inlineStr">
@@ -6489,10 +6489,10 @@
       </c>
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="n">
-        <v>6.09</v>
+        <v>5.97</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>9.91</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr">
@@ -6963,13 +6963,13 @@
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>4621</v>
+        <v>4677</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>11077</v>
+        <v>11115</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -8337,13 +8337,13 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>694</v>
+        <v>704</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>106.7</v>
+        <v>108.3</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -9167,13 +9167,13 @@
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="n">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>97.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>7670</v>
+        <v>7555</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
@@ -10497,10 +10497,10 @@
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>7165</v>
+        <v>7095</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr">
@@ -11487,13 +11487,13 @@
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>3405</v>
+        <v>3378</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -11807,13 +11807,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>26653</v>
+        <v>29394</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>29.1</v>
+        <v>32.1</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -12161,13 +12161,13 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>30153</v>
+        <v>30664</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3632</v>
+        <v>3690</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>77</v>
+        <v>78.3</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -12334,13 +12334,13 @@
       </c>
       <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="13" t="n">
-        <v>3644</v>
+        <v>3611</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
@@ -12511,13 +12511,13 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>114049</v>
+        <v>119608</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2662</v>
+        <v>2792</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>39.9</v>
+        <v>41.8</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -12688,13 +12688,13 @@
         </is>
       </c>
       <c r="G10" s="13" t="n">
-        <v>93960</v>
+        <v>94322</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>1886</v>
+        <v>1892</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
@@ -13034,13 +13034,13 @@
         </is>
       </c>
       <c r="G12" s="13" t="n">
-        <v>57409</v>
+        <v>56604</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
@@ -13354,13 +13354,13 @@
         </is>
       </c>
       <c r="G14" s="13" t="n">
-        <v>136266</v>
+        <v>133008</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>71.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
@@ -13531,13 +13531,13 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>81179</v>
+        <v>81502</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -13700,10 +13700,10 @@
       </c>
       <c r="F16" s="13" t="inlineStr"/>
       <c r="G16" s="13" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="I16" s="13" t="inlineStr"/>
       <c r="J16" s="13" t="inlineStr">
@@ -14822,10 +14822,10 @@
       </c>
       <c r="F24" s="13" t="inlineStr"/>
       <c r="G24" s="13" t="n">
-        <v>45.4</v>
+        <v>47</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>45.4</v>
+        <v>47</v>
       </c>
       <c r="I24" s="13" t="inlineStr"/>
       <c r="J24" s="13" t="inlineStr">
@@ -14951,13 +14951,13 @@
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="n">
-        <v>34.1</v>
+        <v>32.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>62.1</v>
+        <v>59.3</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -16324,10 +16324,10 @@
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I4" s="13" t="inlineStr"/>
       <c r="J4" s="13" t="inlineStr">
@@ -16477,13 +16477,13 @@
       </c>
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="n">
-        <v>4103</v>
+        <v>4497</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>14</v>
+        <v>15.4</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -16823,13 +16823,13 @@
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="n">
-        <v>2231</v>
+        <v>2255</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>977</v>
+        <v>987</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -16996,13 +16996,13 @@
       </c>
       <c r="F8" s="13" t="inlineStr"/>
       <c r="G8" s="13" t="n">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>9655</v>
+        <v>9805.9</v>
       </c>
       <c r="J8" s="13" t="inlineStr">
         <is>
@@ -17800,13 +17800,13 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>3844</v>
+        <v>3791</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -18819,13 +18819,13 @@
         </is>
       </c>
       <c r="G4" s="13" t="n">
-        <v>932345</v>
+        <v>933937</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>2577</v>
+        <v>2582</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -18996,13 +18996,13 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>220532</v>
+        <v>214363</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -19169,13 +19169,13 @@
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="n">
-        <v>53.9</v>
+        <v>52.9</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -20031,13 +20031,13 @@
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="n">
-        <v>3457</v>
+        <v>3473</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>115.7</v>
+        <v>116.2</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -20551,13 +20551,13 @@
       </c>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>205.1</v>
+        <v>205.8</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -20720,13 +20720,13 @@
       </c>
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="n">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>68.7</v>
+        <v>69.5</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -21052,13 +21052,13 @@
       </c>
       <c r="F6" s="13" t="inlineStr"/>
       <c r="G6" s="13" t="n">
-        <v>1363</v>
+        <v>1399</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -21225,10 +21225,10 @@
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr">
@@ -21708,13 +21708,13 @@
       </c>
       <c r="F10" s="13" t="inlineStr"/>
       <c r="G10" s="13" t="n">
-        <v>677</v>
+        <v>730</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>214.1</v>
+        <v>231</v>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
@@ -22518,13 +22518,13 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>20.6</v>
+        <v>19.7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
